--- a/Markowits/Portafolio_Markowitz_Profesor.xlsx
+++ b/Markowits/Portafolio_Markowitz_Profesor.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="78">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -67,6 +67,36 @@
     <t xml:space="preserve">VAR COVAR</t>
   </si>
   <si>
+    <t xml:space="preserve">INVERSA DE VAR COVAR (Σ⁻¹) y constantes de la frontera automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σ⁻¹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u = Σ⁻¹·1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v = Σ⁻¹·μ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a = 1ᵀΣ⁻¹1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con estas 4 constantes la frontera se calcula con fórmulas (ver nota en la hoja Portafolio).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b = 1ᵀΣ⁻¹μ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c = μᵀΣ⁻¹μ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d = a·c − b²</t>
+  </si>
+  <si>
     <t xml:space="preserve">PORTAFOLIO DE INVERSIÓN – MÉTODO DE MARKOWITZ</t>
   </si>
   <si>
@@ -74,6 +104,12 @@
   </si>
   <si>
     <t xml:space="preserve">R ANUAL IPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÉTODO FRONTERA (1 ó 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = fórmulas, se actualiza solo (permite ventas en corto) · 2 = Solver, solo largos (valores fijos)</t>
   </si>
   <si>
     <t xml:space="preserve">EMPRESA</t>
@@ -100,13 +136,16 @@
     <t xml:space="preserve">TLR [RF]</t>
   </si>
   <si>
-    <t xml:space="preserve">← supuesto mío: cámbialo por la tasa libre de riesgo que pida el profe (p. ej. Cetes 28d)</t>
+    <t xml:space="preserve">← Cetes 6.50% (dato que me diste)</t>
   </si>
   <si>
     <t xml:space="preserve">suma</t>
   </si>
   <si>
     <t xml:space="preserve">BETA P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wi = portafolio de mayor Sharpe de la frontera (fórmula). Puedes escribir tus propios pesos encima.</t>
   </si>
   <si>
     <t xml:space="preserve">I SHARPE</t>
@@ -127,7 +166,7 @@
     <t xml:space="preserve">BETA DEL PORTAFOLIO</t>
   </si>
   <si>
-    <t xml:space="preserve">PESOS (Wi) DE CADA PORTAFOLIO DE LA FRONTERA – resultado del Solver (w ≥ 0, Σw = 100%)</t>
+    <t xml:space="preserve">PESOS (Wi) QUE USA LA FRONTERA  =  según el método elegido en I5</t>
   </si>
   <si>
     <t xml:space="preserve">PORTAFOLIO</t>
@@ -136,31 +175,55 @@
     <t xml:space="preserve">SUMA</t>
   </si>
   <si>
+    <t xml:space="preserve">R OBJETIVO</t>
+  </si>
+  <si>
     <t xml:space="preserve">R ANUAL →</t>
   </si>
   <si>
     <t xml:space="preserve">BETA →</t>
   </si>
   <si>
-    <t xml:space="preserve">DATOS AUXILIARES DE LAS GRÁFICAS</t>
+    <t xml:space="preserve">MÉTODO 1 – FRONTERA CON FÓRMULAS (Merton): w = [ (c − b·m)·u + (a·m − b)·v ] / d   · permite ventas en corto</t>
   </si>
   <si>
-    <t xml:space="preserve">CML (SD)</t>
+    <t xml:space="preserve">MÉTODO 2 – RESULTADO DE SOLVER (w ≥ 0, Σw = 100%, mín. SD por rendimiento objetivo) · valores fijos</t>
   </si>
   <si>
-    <t xml:space="preserve">CML (Rend.)</t>
+    <t xml:space="preserve">DATOS AUXILIARES DE LA GRÁFICA (líneas CML, SML y marco punteado)</t>
   </si>
   <si>
-    <t xml:space="preserve">SML (Beta)</t>
+    <t xml:space="preserve">SD del IPC (diaria)</t>
   </si>
   <si>
-    <t xml:space="preserve">SML (Rend.)</t>
+    <t xml:space="preserve">CML: SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CML: Rend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(CML pasa por tu portafolio I7/I12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SML: Beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SML: β·SD IPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SML: Rend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco: SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco: Rend.</t>
   </si>
   <si>
     <t xml:space="preserve">NOTAS</t>
   </si>
   <si>
-    <t xml:space="preserve">• Periodo del profesor (pizarrón): 3 oct 2025 al 2 oct 2026. Este archivo trae del 06/10/2025 al 02/10/2026: falta el cierre del 03/10/2025 (ver nota en el chat).</t>
+    <t xml:space="preserve">• Periodo del profesor (pizarrón): 3 oct 2025 al 2 oct 2026. Este archivo trae del 06/10/2025 al 02/10/2026: falta el cierre del 03/10/2025.</t>
   </si>
   <si>
     <t xml:space="preserve">• Rendimiento diario = LN(precio hoy / precio ayer). R ANUAL = promedio diario × días hábiles (I3). BETA = SLOPE(rend. acción, rend. IPC).</t>
@@ -169,26 +232,38 @@
     <t xml:space="preserve">• VAR COVAR = SD(col) × SD(fila) × Correlación (hoja Matriz). Varianza del portafolio = Wᵀ·Σ·W; SD = √varianza (diaria, como en la plantilla).</t>
   </si>
   <si>
-    <t xml:space="preserve">• I SHARPE = (REND PORTAFOLIO − RF) / SD PORTAFOLIO, tal cual la fórmula de la plantilla (R anual entre SD diaria).</t>
+    <t xml:space="preserve">• I SHARPE = (REND PORTAFOLIO − RF) / SD PORTAFOLIO, tal cual la plantilla (R anual entre SD diaria). RF = Cetes 6.50% (dato del usuario).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Wi (amarillo, D7:D14) está en el portafolio de máximo Sharpe (solo largos). Edítalo y todo se recalcula.</t>
+    <t xml:space="preserve">• Frontera: 9 portafolios con rendimiento objetivo desde la TLR hasta el mayor R ANUAL individual (como la plantilla), cada uno con la mínima SD posible.</t>
   </si>
   <si>
-    <t xml:space="preserve">• La frontera (9 portafolios) va del de mínima varianza al de mayor rendimiento; sus pesos son resultado de Solver (celdas azules).</t>
+    <t xml:space="preserve">• MÉTODO 1 (automático): para un rendimiento objetivo m, los pesos de mínima varianza son w = [(c − b·m)·u + (a·m − b)·v] / d, con</t>
   </si>
   <si>
-    <t xml:space="preserve">  Para repetirlo en Excel: Solver → minimizar la SD del portafolio, cambiando Wi, con Wi ≥ 0, ΣWi = 100% y REND = rendimiento objetivo.</t>
+    <t xml:space="preserve">  u = Σ⁻¹·1, v = Σ⁻¹·μ, a = 1ᵀu, b = 1ᵀv, c = μᵀv, d = a·c − b² (hoja Matriz, filas 41-59). Cambias PRECIOS y todo se recalcula solo.</t>
   </si>
   <si>
-    <t xml:space="preserve">• TLR [RF] es un supuesto mío (no viene de los archivos de Investing).</t>
+    <t xml:space="preserve">  Limitación: permite pesos negativos (venta en corto). Si el profesor pide solo posiciones largas, usa el MÉTODO 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• MÉTODO 2 (Solver): Datos → Solver → minimizar la SD (I12) cambiando D7:D14, con D7:D14 ≥ 0, D15 = 100% y I7 = rendimiento objetivo (R OBJETIVO).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Eso se repite una vez por portafolio; aquí quedan los resultados fijos. Si cambias datos o la TLR, hay que volver a correr Solver.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• El eje Y de la gráfica arranca en 6% (zoom). Si cambias TLR o datos, ajústalo: clic derecho en el eje → Dar formato al eje → Mínimo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Gráfica: línea azul = frontera; roja = CML (de la TLR a tu portafolio); verde = SML (de la TLR por el IPC, con β·SD del IPC en el eje X).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="d&quot; de &quot;mmm&quot; de &quot;yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
@@ -196,17 +271,16 @@
     <numFmt numFmtId="168" formatCode="0.000000"/>
     <numFmt numFmtId="169" formatCode="0.00000000"/>
     <numFmt numFmtId="170" formatCode="0.00E+00"/>
-    <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="0.000%"/>
-    <numFmt numFmtId="173" formatCode="0.00%"/>
-    <numFmt numFmtId="174" formatCode="0.00000E+00"/>
-    <numFmt numFmtId="175" formatCode="0.0%"/>
-    <numFmt numFmtId="176" formatCode="0.00"/>
-    <numFmt numFmtId="177" formatCode="0.000"/>
-    <numFmt numFmtId="178" formatCode="0%"/>
-    <numFmt numFmtId="179" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="173" formatCode="0.000%"/>
+    <numFmt numFmtId="174" formatCode="0.00%"/>
+    <numFmt numFmtId="175" formatCode="0.00000E+00"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="0.00"/>
+    <numFmt numFmtId="178" formatCode="0.000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +338,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -273,7 +354,7 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -305,7 +386,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,6 +403,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
         <bgColor rgb="FFF4B084"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -398,7 +485,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -455,23 +542,107 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,67 +650,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -573,7 +696,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF9C4F48"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -599,7 +722,7 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFC55A11"/>
+      <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF8497B0"/>
       <rgbColor rgb="FF003366"/>
@@ -664,161 +787,24 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Frontera eficiente"</c:f>
+              <c:f>"marco"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Frontera eficiente</c:v>
+                  <c:v>marco</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4472c4"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
-            <a:ln w="21960">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="4472c4"/>
+                <a:srgbClr val="7f7f7f"/>
               </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4472c4"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0%" sourceLinked="1"/>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="r"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Portafolio!$I$19:$I$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000000</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>0.00942791742359553</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.00947790254116003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.00962630301690294</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.00987145155821254</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.0102167406893086</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.0106534864614822</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.0112037808765303</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.0127432406890865</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.0172079118776168</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Portafolio!$J$19:$J$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>-0.0945371943414465</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.0724967295697424</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.0504560293241027</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.0284152952219226</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.00637486490657266</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.0156656798971437</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.0377064173428471</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.0597469068206446</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.0817875821358763</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Línea del mercado de capitales (CML)"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Línea del mercado de capitales (CML)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="c00000"/>
-            </a:solidFill>
-            <a:ln w="21960">
-              <a:solidFill>
-                <a:srgbClr val="c00000"/>
-              </a:solidFill>
+              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
@@ -852,7 +838,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Portafolio!$H$60:$H$62</c:f>
+              <c:f>Portafolio!$N$90:$N$92</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="3"/>
@@ -860,28 +846,153 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0172079118776168</c:v>
+                  <c:v>0.0122217948332109</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0275326590041868</c:v>
+                  <c:v>0.0122217948332109</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Portafolio!$I$60:$I$62</c:f>
+              <c:f>Portafolio!$O$90:$O$92</c:f>
               <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
+                <c:formatCode>0.000%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.07</c:v>
+                  <c:v>0.0817875821358763</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0817875821358763</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0888601314174021</c:v>
+                  <c:v>0.065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Security Market Line"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Security Market Line</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="548235"/>
+            </a:solidFill>
+            <a:ln w="21960">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Portafolio!$L$90:$L$92</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0106681513686276</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0160022270529414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Portafolio!$M$90:$M$92</c:f>
+              <c:numCache>
+                <c:formatCode>0.000%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.065</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0668941515629918</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0678412273444877</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -893,50 +1004,81 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Acciones"</c:f>
+              <c:f>"Capital Market Line"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Acciones</c:v>
+                  <c:v>Capital Market Line</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c55a11"/>
+              <a:srgbClr val="c00000"/>
             </a:solidFill>
-            <a:ln w="28440">
-              <a:noFill/>
+            <a:ln w="21960">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="c55a11"/>
-              </a:solidFill>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -946,92 +1088,374 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Matriz!$E$7:$E$14</c:f>
+              <c:f>Portafolio!$H$90:$H$92</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.0136488291094263</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0156184064873583</c:v>
+                  <c:v>0.0122217948332109</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0154076296579846</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.0177452623343298</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.0206484049274787</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.0172079118776168</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.0251092781521838</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.0137902936697508</c:v>
+                  <c:v>0.0183326922498164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Portafolio!$E$7:$E$14</c:f>
+              <c:f>Portafolio!$I$90:$I$92</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.0362443957061986</c:v>
+                  <c:v>0.065</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.23642948794273</c:v>
+                  <c:v>0.0817875821358763</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.00998135039076667</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.167384055383504</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.0579153426562407</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.0817875821358763</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-0.133752464024379</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-0.1702800898151</c:v>
+                  <c:v>0.0901813732038144</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="74117970"/>
-        <c:axId val="23313309"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Frontera eficiente"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Frontera eficiente</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472c4"/>
+            </a:solidFill>
+            <a:ln w="28080">
+              <a:solidFill>
+                <a:srgbClr val="4472c4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472c4"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="7"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="4472c4"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="7"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="4472c4"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="7"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="4472c4"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="7"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="4472c4"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="7"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="4472c4"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Portafolio!$I$19:$I$27</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.0117644715517125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0118200679176229</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0118761254022205</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0119326375067375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.0119895978027211</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0120469999327929</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.0121048376113144</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.0121631046249613</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.0122217948332109</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Portafolio!$J$19:$J$27</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.065</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0670984477669845</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.069196895533969</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0712953433009536</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.0733937910679381</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0754922388349227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.0775906866019072</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.0796891343688918</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.0817875821358763</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="31193797"/>
+        <c:axId val="78387778"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="74117970"/>
+        <c:axId val="31193797"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1092,27 +1516,18 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23313309"/>
+        <c:crossAx val="78387778"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="23313309"/>
+        <c:axId val="78387778"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.06"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1147,7 +1562,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
@@ -1173,7 +1588,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74117970"/>
+        <c:crossAx val="31193797"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1184,502 +1599,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Security Market Line</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"SML"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SML</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="548235"/>
-            </a:solidFill>
-            <a:ln w="21960">
-              <a:solidFill>
-                <a:srgbClr val="548235"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Portafolio!$J$60:$J$62</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Portafolio!$K$60:$K$62</c:f>
-              <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.07</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.0668941515629918</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.0637883031259836</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Acciones"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Acciones</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="c55a11"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="c55a11"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Portafolio!$F$7:$F$14</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000000</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.724158085195439</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.541882805896259</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.770222706343104</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.797170266661248</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.28874432295921</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.14498888583895</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.525886028942383</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.55742145075492</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Portafolio!$E$7:$E$14</c:f>
-              <c:numCache>
-                <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.0362443957061986</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.23642948794273</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.00998135039076667</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.167384055383504</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.0579153426562407</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.0817875821358763</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-0.133752464024379</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-0.1702800898151</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:axId val="61253626"/>
-        <c:axId val="60979430"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="61253626"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Beta</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="60979430"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="60979430"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Rendimiento anual</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0%" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="61253626"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -1701,16 +1620,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>190440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>368640</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>532080</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>81720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1718,42 +1637,12 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="12687480" y="380880"/>
-        <a:ext cx="6479640" cy="3419640"/>
+        <a:off x="18444240" y="380880"/>
+        <a:ext cx="7199640" cy="3959640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>368640</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="12687480" y="4610160"/>
-        <a:ext cx="6479640" cy="3419640"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -20516,7 +20405,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C2:M39"/>
+  <dimension ref="C2:M61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
@@ -21350,6 +21239,536 @@
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="14"/>
+      <c r="D41" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C42" s="14"/>
+      <c r="D42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="14"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="14"/>
+      <c r="D43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <f aca="false" t="array" ref="E43:L50">MINVERSE(E31:L38)</f>
+        <v>8124.93026014866</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>-1100.3179973317</v>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>-606.87166014191</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>-1299.28744263378</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>-542.572586489169</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>-1512.66730488964</v>
+      </c>
+      <c r="K43" s="17" t="n">
+        <v>353.556031987372</v>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>-1263.48687319992</v>
+      </c>
+      <c r="M43" s="14"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C44" s="14"/>
+      <c r="D44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-1100.3179973317</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>4683.53723993584</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>-296.564925778498</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>-391.82293237838</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>-20.1583947870396</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>22.1265951797586</v>
+      </c>
+      <c r="K44" s="17" t="n">
+        <v>-60.1599686309828</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>-619.822302534489</v>
+      </c>
+      <c r="M44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C45" s="14"/>
+      <c r="D45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-606.871660141911</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>-296.564925778498</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>5307.63794659865</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>-465.59005431282</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>-624.15887147193</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>-675.16161311622</v>
+      </c>
+      <c r="K45" s="17" t="n">
+        <v>-112.633683386292</v>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>-734.898447061114</v>
+      </c>
+      <c r="M45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C46" s="14"/>
+      <c r="D46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-1299.28744263378</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>-391.82293237838</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>-465.59005431282</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>4119.20813033379</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>-264.785511736554</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>-368.068073144331</v>
+      </c>
+      <c r="K46" s="17" t="n">
+        <v>-364.688219583009</v>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>-358.606923230572</v>
+      </c>
+      <c r="M46" s="14"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C47" s="14"/>
+      <c r="D47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>-542.572586489169</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>-20.1583947870396</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>-624.15887147193</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>-264.785511736554</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>2995.65017554776</v>
+      </c>
+      <c r="J47" s="17" t="n">
+        <v>-743.188904029322</v>
+      </c>
+      <c r="K47" s="17" t="n">
+        <v>-282.831821989772</v>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>-218.308395753322</v>
+      </c>
+      <c r="M47" s="14"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C48" s="14"/>
+      <c r="D48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-1512.66730488964</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>22.1265951797586</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>-675.16161311622</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>-368.068073144331</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>-743.188904029322</v>
+      </c>
+      <c r="J48" s="17" t="n">
+        <v>4793.88095948965</v>
+      </c>
+      <c r="K48" s="17" t="n">
+        <v>-295.242645401249</v>
+      </c>
+      <c r="L48" s="17" t="n">
+        <v>-726.390731546739</v>
+      </c>
+      <c r="M48" s="14"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C49" s="14"/>
+      <c r="D49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>353.556031987372</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>-60.1599686309828</v>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>-112.633683386292</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>-364.688219583009</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>-282.831821989772</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>-295.242645401249</v>
+      </c>
+      <c r="K49" s="17" t="n">
+        <v>1717.47182466778</v>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>33.5097343619311</v>
+      </c>
+      <c r="M49" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C50" s="14"/>
+      <c r="D50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>-1263.48687319992</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>-619.822302534489</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>-734.898447061114</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>-358.606923230572</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>-218.308395753322</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>-726.390731546739</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>33.5097343619311</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>6586.30680117062</v>
+      </c>
+      <c r="M50" s="14"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C52" s="14"/>
+      <c r="D52" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C53" s="14"/>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <f aca="false">SUM($E43:$L43)</f>
+        <v>2153.28242744992</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <f aca="false">SUM($E44:$L44)</f>
+        <v>2216.81731367451</v>
+      </c>
+      <c r="G53" s="18" t="n">
+        <f aca="false">SUM($E45:$L45)</f>
+        <v>1791.75869132987</v>
+      </c>
+      <c r="H53" s="18" t="n">
+        <f aca="false">SUM($E46:$L46)</f>
+        <v>606.358973314351</v>
+      </c>
+      <c r="I53" s="18" t="n">
+        <f aca="false">SUM($E47:$L47)</f>
+        <v>299.645689290651</v>
+      </c>
+      <c r="J53" s="18" t="n">
+        <f aca="false">SUM($E48:$L48)</f>
+        <v>495.288282541914</v>
+      </c>
+      <c r="K53" s="18" t="n">
+        <f aca="false">SUM($E49:$L49)</f>
+        <v>988.981252025779</v>
+      </c>
+      <c r="L53" s="18" t="n">
+        <f aca="false">SUM($E50:$L50)</f>
+        <v>2698.30286220639</v>
+      </c>
+      <c r="M53" s="14"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C54" s="14"/>
+      <c r="D54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E43:$L43,Portafolio!$I$46:$P$46)</f>
+        <v>778.77039978657</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E44:$L44,Portafolio!$I$46:$P$46)</f>
+        <v>-970.349737556576</v>
+      </c>
+      <c r="G54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E45:$L45,Portafolio!$I$46:$P$46)</f>
+        <v>227.866137934598</v>
+      </c>
+      <c r="H54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E46:$L46,Portafolio!$I$46:$P$46)</f>
+        <v>-584.187346575605</v>
+      </c>
+      <c r="I54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E47:$L47,Portafolio!$I$46:$P$46)</f>
+        <v>210.905256995001</v>
+      </c>
+      <c r="J54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E48:$L48,Portafolio!$I$46:$P$46)</f>
+        <v>507.029813175494</v>
+      </c>
+      <c r="K54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E49:$L49,Portafolio!$I$46:$P$46)</f>
+        <v>-188.992840823536</v>
+      </c>
+      <c r="L54" s="18" t="n">
+        <f aca="false">SUMPRODUCT($E50:$L50,Portafolio!$I$46:$P$46)</f>
+        <v>-1044.6123167577</v>
+      </c>
+      <c r="M54" s="14"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C56" s="14"/>
+      <c r="D56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <f aca="false">SUM(E53:L53)</f>
+        <v>11250.4354918334</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C57" s="14"/>
+      <c r="D57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <f aca="false">SUM(E54:L54)</f>
+        <v>-1063.57063382175</v>
+      </c>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C58" s="14"/>
+      <c r="D58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <f aca="false">SUMPRODUCT(E54:L54,Portafolio!$I$46:$P$46)</f>
+        <v>614.541743028343</v>
+      </c>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C59" s="14"/>
+      <c r="D59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <f aca="false">E56*E58-E57^2</f>
+        <v>5782679.74385122</v>
+      </c>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -21367,7 +21786,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:Q73"/>
+  <dimension ref="B2:R107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="3"/>
@@ -21375,57 +21794,69 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="13" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H3" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="15" t="n">
+      <c r="H3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>252</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H4" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="17" t="n">
+      <c r="H4" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$J$3:$J$251)*$I$3</f>
         <v>0.0668941515629918</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>20</v>
+      <c r="C6" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="17" t="n">
+      <c r="D7" s="26" t="n">
+        <f aca="false">INDEX(I$48:I$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>0.528379419679543</v>
+      </c>
+      <c r="E7" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$B$3:$B$251)*$I$3</f>
         <v>0.0362443957061986</v>
       </c>
@@ -21433,10 +21864,10 @@
         <f aca="false">SLOPE(RENDIMIENTOS!$B$3:$B$251,RENDIMIENTOS!$J$3:$J$251)</f>
         <v>0.724158085195439</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="17" t="n">
+      <c r="H7" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="23" t="n">
         <f aca="false">SUMPRODUCT(D7:D14,E7:E14)</f>
         <v>0.0817875821358763</v>
       </c>
@@ -21445,10 +21876,11 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
+      <c r="D8" s="26" t="n">
+        <f aca="false">INDEX(J$48:J$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>-0.0639388785210929</v>
+      </c>
+      <c r="E8" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$C$3:$C$251)*$I$3</f>
         <v>-0.23642948794273</v>
       </c>
@@ -21461,10 +21893,11 @@
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="17" t="n">
+      <c r="D9" s="26" t="n">
+        <f aca="false">INDEX(K$48:K$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>0.295536307645177</v>
+      </c>
+      <c r="E9" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$D$3:$D$251)*$I$3</f>
         <v>0.00998135039076667</v>
       </c>
@@ -21472,22 +21905,23 @@
         <f aca="false">SLOPE(RENDIMIENTOS!$D$3:$D$251,RENDIMIENTOS!$J$3:$J$251)</f>
         <v>0.770222706343104</v>
       </c>
-      <c r="H9" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="19" t="n">
+      <c r="H9" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="27" t="n">
         <f aca="false">SUMPRODUCT(MMULT(Matriz!$E$31:$L$38,D7:D14),D7:D14)</f>
-        <v>0.000296112231187824</v>
+        <v>0.000149372268945101</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="17" t="n">
+      <c r="D10" s="26" t="n">
+        <f aca="false">INDEX(L$48:L$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>-0.126841528615483</v>
+      </c>
+      <c r="E10" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$E$3:$E$251)*$I$3</f>
         <v>-0.167384055383504</v>
       </c>
@@ -21500,10 +21934,11 @@
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="17" t="n">
+      <c r="D11" s="26" t="n">
+        <f aca="false">INDEX(M$48:M$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>0.108701553907201</v>
+      </c>
+      <c r="E11" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$F$3:$F$251)*$I$3</f>
         <v>0.0579153426562407</v>
       </c>
@@ -21516,10 +21951,11 @@
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="D12" s="26" t="n">
+        <f aca="false">INDEX(N$48:N$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>0.234019934391866</v>
+      </c>
+      <c r="E12" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$G$3:$G$251)*$I$3</f>
         <v>0.0817875821358763</v>
       </c>
@@ -21527,22 +21963,23 @@
         <f aca="false">SLOPE(RENDIMIENTOS!$G$3:$G$251,RENDIMIENTOS!$J$3:$J$251)</f>
         <v>1.14498888583895</v>
       </c>
-      <c r="H12" s="20" t="s">
-        <v>23</v>
+      <c r="H12" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="I12" s="8" t="n">
         <f aca="false">SQRT(I9)</f>
-        <v>0.0172079118776168</v>
+        <v>0.0122217948332109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="17" t="n">
+      <c r="D13" s="26" t="n">
+        <f aca="false">INDEX(O$48:O$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>0.055145786112025</v>
+      </c>
+      <c r="E13" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$H$3:$H$251)*$I$3</f>
         <v>-0.133752464024379</v>
       </c>
@@ -21555,10 +21992,11 @@
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="17" t="n">
+      <c r="D14" s="26" t="n">
+        <f aca="false">INDEX(P$48:P$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
+        <v>-0.0310025945992354</v>
+      </c>
+      <c r="E14" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$I$3:$I$251)*$I$3</f>
         <v>-0.1702800898151</v>
       </c>
@@ -21566,771 +22004,1768 @@
         <f aca="false">SLOPE(RENDIMIENTOS!$I$3:$I$251,RENDIMIENTOS!$J$3:$J$251)</f>
         <v>0.55742145075492</v>
       </c>
-      <c r="H14" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>25</v>
+      <c r="H14" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="D15" s="29" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="24" t="n">
+      <c r="E15" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="31" t="n">
         <f aca="false">SUMPRODUCT(D7:D14,F7:F14)</f>
-        <v>1.14498888583895</v>
+        <v>0.894254951070821</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H16" s="16" t="s">
-        <v>28</v>
+      <c r="C16" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="I16" s="9" t="n">
         <f aca="false">+(I7-I14)/I12</f>
-        <v>0.685009443313633</v>
+        <v>1.37357747900157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="20" t="s">
-        <v>33</v>
+      <c r="H18" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I48:$P48,Matriz!$E$31:$L$38),$I48:$P48))</f>
-        <v>0.00942791742359553</v>
-      </c>
-      <c r="J19" s="27" t="n">
+        <v>0.0117644715517125</v>
+      </c>
+      <c r="J19" s="35" t="n">
         <f aca="false">SUMPRODUCT($I48:$P48,$I$46:$P$46)</f>
-        <v>-0.0945371943414465</v>
+        <v>0.065</v>
       </c>
       <c r="K19" s="9" t="n">
         <f aca="false">(J19-$I$14)/I19</f>
-        <v>-17.4521251034353</v>
+        <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
         <f aca="false">SUMPRODUCT($I48:$P48,$I$47:$P$47)</f>
-        <v>0.675666853759229</v>
+        <v>0.873442556027565</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I20" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I49:$P49,Matriz!$E$31:$L$38),$I49:$P49))</f>
-        <v>0.00947790254116003</v>
-      </c>
-      <c r="J20" s="27" t="n">
+        <v>0.0118200679176229</v>
+      </c>
+      <c r="J20" s="35" t="n">
         <f aca="false">SUMPRODUCT($I49:$P49,$I$46:$P$46)</f>
-        <v>-0.0724967295697424</v>
+        <v>0.0670984477669845</v>
       </c>
       <c r="K20" s="9" t="n">
         <f aca="false">(J20-$I$14)/I20</f>
-        <v>-15.0346270127717</v>
+        <v>0.1775326319281</v>
       </c>
       <c r="L20" s="9" t="n">
         <f aca="false">SUMPRODUCT($I49:$P49,$I$47:$P$47)</f>
-        <v>0.702986093996964</v>
+        <v>0.876044105407972</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H21" s="25" t="n">
+      <c r="H21" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="26" t="n">
+      <c r="I21" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I50:$P50,Matriz!$E$31:$L$38),$I50:$P50))</f>
-        <v>0.00962630301690294</v>
-      </c>
-      <c r="J21" s="27" t="n">
+        <v>0.0118761254022205</v>
+      </c>
+      <c r="J21" s="35" t="n">
         <f aca="false">SUMPRODUCT($I50:$P50,$I$46:$P$46)</f>
-        <v>-0.0504560293241027</v>
+        <v>0.069196895533969</v>
       </c>
       <c r="K21" s="9" t="n">
         <f aca="false">(J21-$I$14)/I21</f>
-        <v>-12.5132181183776</v>
+        <v>0.35338929085275</v>
       </c>
       <c r="L21" s="9" t="n">
         <f aca="false">SUMPRODUCT($I50:$P50,$I$47:$P$47)</f>
-        <v>0.730306794122786</v>
+        <v>0.878645654788379</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H22" s="25" t="n">
+      <c r="H22" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I22" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I51:$P51,Matriz!$E$31:$L$38),$I51:$P51))</f>
-        <v>0.00987145155821254</v>
-      </c>
-      <c r="J22" s="27" t="n">
+        <v>0.0119326375067375</v>
+      </c>
+      <c r="J22" s="35" t="n">
         <f aca="false">SUMPRODUCT($I51:$P51,$I$46:$P$46)</f>
-        <v>-0.0284152952219226</v>
+        <v>0.0712953433009536</v>
       </c>
       <c r="K22" s="9" t="n">
         <f aca="false">(J22-$I$14)/I22</f>
-        <v>-9.96968831195308</v>
+        <v>0.527573497259014</v>
       </c>
       <c r="L22" s="9" t="n">
         <f aca="false">SUMPRODUCT($I51:$P51,$I$47:$P$47)</f>
-        <v>0.761002918234305</v>
+        <v>0.881247204168786</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H23" s="25" t="n">
+      <c r="H23" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="I23" s="26" t="n">
+      <c r="I23" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I52:$P52,Matriz!$E$31:$L$38),$I52:$P52))</f>
-        <v>0.0102167406893086</v>
-      </c>
-      <c r="J23" s="27" t="n">
+        <v>0.0119895978027211</v>
+      </c>
+      <c r="J23" s="35" t="n">
         <f aca="false">SUMPRODUCT($I52:$P52,$I$46:$P$46)</f>
-        <v>-0.00637486490657266</v>
+        <v>0.0733937910679381</v>
       </c>
       <c r="K23" s="9" t="n">
         <f aca="false">(J23-$I$14)/I23</f>
-        <v>-7.47546279475372</v>
+        <v>0.700089461385697</v>
       </c>
       <c r="L23" s="9" t="n">
         <f aca="false">SUMPRODUCT($I52:$P52,$I$47:$P$47)</f>
-        <v>0.793821167773928</v>
+        <v>0.883848753549193</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H24" s="25" t="n">
+      <c r="H24" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I53:$P53,Matriz!$E$31:$L$38),$I53:$P53))</f>
-        <v>0.0106534864614822</v>
-      </c>
-      <c r="J24" s="27" t="n">
+        <v>0.0120469999327929</v>
+      </c>
+      <c r="J24" s="35" t="n">
         <f aca="false">SUMPRODUCT($I53:$P53,$I$46:$P$46)</f>
-        <v>0.0156656798971437</v>
+        <v>0.0754922388349227</v>
       </c>
       <c r="K24" s="9" t="n">
         <f aca="false">(J24-$I$14)/I24</f>
-        <v>-5.10014447376477</v>
+        <v>0.870942051419955</v>
       </c>
       <c r="L24" s="9" t="n">
         <f aca="false">SUMPRODUCT($I53:$P53,$I$47:$P$47)</f>
-        <v>0.826644868845408</v>
+        <v>0.8864503029296</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H25" s="25" t="n">
+      <c r="H25" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I54:$P54,Matriz!$E$31:$L$38),$I54:$P54))</f>
-        <v>0.0112037808765303</v>
-      </c>
-      <c r="J25" s="27" t="n">
+        <v>0.0121048376113144</v>
+      </c>
+      <c r="J25" s="35" t="n">
         <f aca="false">SUMPRODUCT($I54:$P54,$I$46:$P$46)</f>
-        <v>0.0377064173428471</v>
+        <v>0.0775906866019072</v>
       </c>
       <c r="K25" s="9" t="n">
         <f aca="false">(J25-$I$14)/I25</f>
-        <v>-2.88238256469312</v>
+        <v>1.04013676235844</v>
       </c>
       <c r="L25" s="9" t="n">
         <f aca="false">SUMPRODUCT($I54:$P54,$I$47:$P$47)</f>
-        <v>0.875940107248563</v>
+        <v>0.889051852310007</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="25" t="n">
+      <c r="H26" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I55:$P55,Matriz!$E$31:$L$38),$I55:$P55))</f>
-        <v>0.0127432406890865</v>
-      </c>
-      <c r="J26" s="27" t="n">
+        <v>0.0121631046249613</v>
+      </c>
+      <c r="J26" s="35" t="n">
         <f aca="false">SUMPRODUCT($I55:$P55,$I$46:$P$46)</f>
-        <v>0.0597469068206446</v>
+        <v>0.0796891343688918</v>
       </c>
       <c r="K26" s="9" t="n">
         <f aca="false">(J26-$I$14)/I26</f>
-        <v>-0.804590718288508</v>
+        <v>1.20767968555878</v>
       </c>
       <c r="L26" s="9" t="n">
         <f aca="false">SUMPRODUCT($I55:$P55,$I$47:$P$47)</f>
-        <v>1.00691646370105</v>
+        <v>0.891653401690414</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="25" t="n">
+      <c r="H27" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I56:$P56,Matriz!$E$31:$L$38),$I56:$P56))</f>
-        <v>0.0172079118776168</v>
-      </c>
-      <c r="J27" s="27" t="n">
+        <v>0.0122217948332109</v>
+      </c>
+      <c r="J27" s="35" t="n">
         <f aca="false">SUMPRODUCT($I56:$P56,$I$46:$P$46)</f>
         <v>0.0817875821358763</v>
       </c>
       <c r="K27" s="9" t="n">
         <f aca="false">(J27-$I$14)/I27</f>
-        <v>0.685009443313633</v>
+        <v>1.37357747900157</v>
       </c>
       <c r="L27" s="9" t="n">
         <f aca="false">SUMPRODUCT($I56:$P56,$I$47:$P$47)</f>
-        <v>1.14498888583895</v>
+        <v>0.894254951070821</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H43" s="28" t="s">
-        <v>34</v>
+      <c r="H43" s="36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H45" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I45" s="16" t="s">
+      <c r="H45" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="I45" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="J45" s="16" t="s">
+      <c r="J45" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="K45" s="16" t="s">
+      <c r="K45" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="16" t="s">
+      <c r="L45" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="16" t="s">
+      <c r="M45" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N45" s="16" t="s">
+      <c r="N45" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O45" s="16" t="s">
+      <c r="O45" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="P45" s="16" t="s">
+      <c r="P45" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="16" t="s">
-        <v>36</v>
+      <c r="Q45" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R45" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H46" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I46" s="29" t="n">
+        <v>51</v>
+      </c>
+      <c r="I46" s="37" t="n">
         <f aca="false">$E$7</f>
         <v>0.0362443957061986</v>
       </c>
-      <c r="J46" s="29" t="n">
+      <c r="J46" s="37" t="n">
         <f aca="false">$E$8</f>
         <v>-0.23642948794273</v>
       </c>
-      <c r="K46" s="29" t="n">
+      <c r="K46" s="37" t="n">
         <f aca="false">$E$9</f>
         <v>0.00998135039076667</v>
       </c>
-      <c r="L46" s="29" t="n">
+      <c r="L46" s="37" t="n">
         <f aca="false">$E$10</f>
         <v>-0.167384055383504</v>
       </c>
-      <c r="M46" s="29" t="n">
+      <c r="M46" s="37" t="n">
         <f aca="false">$E$11</f>
         <v>0.0579153426562407</v>
       </c>
-      <c r="N46" s="29" t="n">
+      <c r="N46" s="37" t="n">
         <f aca="false">$E$12</f>
         <v>0.0817875821358763</v>
       </c>
-      <c r="O46" s="29" t="n">
+      <c r="O46" s="37" t="n">
         <f aca="false">$E$13</f>
         <v>-0.133752464024379</v>
       </c>
-      <c r="P46" s="29" t="n">
+      <c r="P46" s="37" t="n">
         <f aca="false">$E$14</f>
         <v>-0.1702800898151</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I47" s="30" t="n">
+        <v>52</v>
+      </c>
+      <c r="I47" s="38" t="n">
         <f aca="false">$F$7</f>
         <v>0.724158085195439</v>
       </c>
-      <c r="J47" s="30" t="n">
+      <c r="J47" s="38" t="n">
         <f aca="false">$F$8</f>
         <v>0.541882805896259</v>
       </c>
-      <c r="K47" s="30" t="n">
+      <c r="K47" s="38" t="n">
         <f aca="false">$F$9</f>
         <v>0.770222706343104</v>
       </c>
-      <c r="L47" s="30" t="n">
+      <c r="L47" s="38" t="n">
         <f aca="false">$F$10</f>
         <v>0.797170266661248</v>
       </c>
-      <c r="M47" s="30" t="n">
+      <c r="M47" s="38" t="n">
         <f aca="false">$F$11</f>
         <v>1.28874432295921</v>
       </c>
-      <c r="N47" s="30" t="n">
+      <c r="N47" s="38" t="n">
         <f aca="false">$F$12</f>
         <v>1.14498888583895</v>
       </c>
-      <c r="O47" s="30" t="n">
+      <c r="O47" s="38" t="n">
         <f aca="false">$F$13</f>
         <v>0.525886028942383</v>
       </c>
-      <c r="P47" s="30" t="n">
+      <c r="P47" s="38" t="n">
         <f aca="false">$F$14</f>
         <v>0.55742145075492</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H48" s="25" t="n">
+      <c r="H48" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="31" t="n">
-        <v>0.191381</v>
-      </c>
-      <c r="J48" s="31" t="n">
-        <v>0.197026</v>
-      </c>
-      <c r="K48" s="31" t="n">
-        <v>0.159214</v>
-      </c>
-      <c r="L48" s="31" t="n">
-        <v>0.053885</v>
-      </c>
-      <c r="M48" s="31" t="n">
-        <v>0.026641</v>
-      </c>
-      <c r="N48" s="31" t="n">
-        <v>0.044055</v>
-      </c>
-      <c r="O48" s="31" t="n">
-        <v>0.087905</v>
-      </c>
-      <c r="P48" s="31" t="n">
-        <v>0.239894</v>
-      </c>
-      <c r="Q48" s="32" t="n">
+      <c r="I48" s="39" t="n">
+        <f aca="false">IF($I$5=1,I61,I74)</f>
+        <v>0.496295525197577</v>
+      </c>
+      <c r="J48" s="39" t="n">
+        <f aca="false">IF($I$5=1,J61,J74)</f>
+        <v>-0.0390910816512745</v>
+      </c>
+      <c r="K48" s="39" t="n">
+        <f aca="false">IF($I$5=1,K61,K74)</f>
+        <v>0.282561702048613</v>
+      </c>
+      <c r="L48" s="39" t="n">
+        <f aca="false">IF($I$5=1,L61,L74)</f>
+        <v>-0.109633648084208</v>
+      </c>
+      <c r="M48" s="39" t="n">
+        <f aca="false">IF($I$5=1,M61,M74)</f>
+        <v>0.100888000075036</v>
+      </c>
+      <c r="N48" s="39" t="n">
+        <f aca="false">IF($I$5=1,N61,N74)</f>
+        <v>0.215930609615409</v>
+      </c>
+      <c r="O48" s="39" t="n">
+        <f aca="false">IF($I$5=1,O61,O74)</f>
+        <v>0.0582648563133571</v>
+      </c>
+      <c r="P48" s="39" t="n">
+        <f aca="false">IF($I$5=1,P61,P74)</f>
+        <v>-0.00521596351451034</v>
+      </c>
+      <c r="Q48" s="40" t="n">
         <f aca="false">SUM(I48:P48)</f>
-        <v>1.000001</v>
+        <v>1</v>
+      </c>
+      <c r="R48" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*0/8</f>
+        <v>0.065</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H49" s="25" t="n">
+      <c r="H49" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="31" t="n">
-        <v>0.233508</v>
-      </c>
-      <c r="J49" s="31" t="n">
-        <v>0.164402</v>
-      </c>
-      <c r="K49" s="31" t="n">
-        <v>0.176268</v>
-      </c>
-      <c r="L49" s="31" t="n">
-        <v>0.031296</v>
-      </c>
-      <c r="M49" s="31" t="n">
-        <v>0.036896</v>
-      </c>
-      <c r="N49" s="31" t="n">
-        <v>0.06779</v>
-      </c>
-      <c r="O49" s="31" t="n">
-        <v>0.08381</v>
-      </c>
-      <c r="P49" s="31" t="n">
-        <v>0.206031</v>
-      </c>
-      <c r="Q49" s="32" t="n">
+      <c r="I49" s="39" t="n">
+        <f aca="false">IF($I$5=1,I62,I75)</f>
+        <v>0.500306012007823</v>
+      </c>
+      <c r="J49" s="39" t="n">
+        <f aca="false">IF($I$5=1,J62,J75)</f>
+        <v>-0.0421970562600018</v>
+      </c>
+      <c r="K49" s="39" t="n">
+        <f aca="false">IF($I$5=1,K62,K75)</f>
+        <v>0.284183527748183</v>
+      </c>
+      <c r="L49" s="39" t="n">
+        <f aca="false">IF($I$5=1,L62,L75)</f>
+        <v>-0.111784633150617</v>
+      </c>
+      <c r="M49" s="39" t="n">
+        <f aca="false">IF($I$5=1,M62,M75)</f>
+        <v>0.101864694304057</v>
+      </c>
+      <c r="N49" s="39" t="n">
+        <f aca="false">IF($I$5=1,N62,N75)</f>
+        <v>0.218191775212466</v>
+      </c>
+      <c r="O49" s="39" t="n">
+        <f aca="false">IF($I$5=1,O62,O75)</f>
+        <v>0.0578749725381906</v>
+      </c>
+      <c r="P49" s="39" t="n">
+        <f aca="false">IF($I$5=1,P62,P75)</f>
+        <v>-0.00843929240010092</v>
+      </c>
+      <c r="Q49" s="40" t="n">
         <f aca="false">SUM(I49:P49)</f>
-        <v>1.000001</v>
+        <v>1</v>
+      </c>
+      <c r="R49" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*1/8</f>
+        <v>0.0670984477669845</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H50" s="25" t="n">
+      <c r="H50" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="I50" s="31" t="n">
-        <v>0.275635</v>
-      </c>
-      <c r="J50" s="31" t="n">
-        <v>0.131786</v>
-      </c>
-      <c r="K50" s="31" t="n">
-        <v>0.193321</v>
-      </c>
-      <c r="L50" s="31" t="n">
-        <v>0.008709</v>
-      </c>
-      <c r="M50" s="31" t="n">
-        <v>0.047152</v>
-      </c>
-      <c r="N50" s="31" t="n">
-        <v>0.091527</v>
-      </c>
-      <c r="O50" s="31" t="n">
-        <v>0.079716</v>
-      </c>
-      <c r="P50" s="31" t="n">
-        <v>0.172154</v>
-      </c>
-      <c r="Q50" s="32" t="n">
+      <c r="I50" s="39" t="n">
+        <f aca="false">IF($I$5=1,I63,I76)</f>
+        <v>0.504316498818069</v>
+      </c>
+      <c r="J50" s="39" t="n">
+        <f aca="false">IF($I$5=1,J63,J76)</f>
+        <v>-0.0453030308687291</v>
+      </c>
+      <c r="K50" s="39" t="n">
+        <f aca="false">IF($I$5=1,K63,K76)</f>
+        <v>0.285805353447754</v>
+      </c>
+      <c r="L50" s="39" t="n">
+        <f aca="false">IF($I$5=1,L63,L76)</f>
+        <v>-0.113935618217027</v>
+      </c>
+      <c r="M50" s="39" t="n">
+        <f aca="false">IF($I$5=1,M63,M76)</f>
+        <v>0.102841388533077</v>
+      </c>
+      <c r="N50" s="39" t="n">
+        <f aca="false">IF($I$5=1,N63,N76)</f>
+        <v>0.220452940809523</v>
+      </c>
+      <c r="O50" s="39" t="n">
+        <f aca="false">IF($I$5=1,O63,O76)</f>
+        <v>0.0574850887630241</v>
+      </c>
+      <c r="P50" s="39" t="n">
+        <f aca="false">IF($I$5=1,P63,P76)</f>
+        <v>-0.0116626212856916</v>
+      </c>
+      <c r="Q50" s="40" t="n">
         <f aca="false">SUM(I50:P50)</f>
         <v>1</v>
       </c>
+      <c r="R50" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*2/8</f>
+        <v>0.0691968955339691</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H51" s="25" t="n">
+      <c r="H51" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="I51" s="31" t="n">
-        <v>0.316177</v>
-      </c>
-      <c r="J51" s="31" t="n">
-        <v>0.094169</v>
-      </c>
-      <c r="K51" s="31" t="n">
-        <v>0.209757</v>
-      </c>
-      <c r="L51" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="31" t="n">
-        <v>0.057268</v>
-      </c>
-      <c r="N51" s="31" t="n">
-        <v>0.115952</v>
-      </c>
-      <c r="O51" s="31" t="n">
-        <v>0.073604</v>
-      </c>
-      <c r="P51" s="31" t="n">
-        <v>0.133073</v>
-      </c>
-      <c r="Q51" s="32" t="n">
+      <c r="I51" s="39" t="n">
+        <f aca="false">IF($I$5=1,I64,I77)</f>
+        <v>0.508326985628314</v>
+      </c>
+      <c r="J51" s="39" t="n">
+        <f aca="false">IF($I$5=1,J64,J77)</f>
+        <v>-0.0484090054774564</v>
+      </c>
+      <c r="K51" s="39" t="n">
+        <f aca="false">IF($I$5=1,K64,K77)</f>
+        <v>0.287427179147325</v>
+      </c>
+      <c r="L51" s="39" t="n">
+        <f aca="false">IF($I$5=1,L64,L77)</f>
+        <v>-0.116086603283436</v>
+      </c>
+      <c r="M51" s="39" t="n">
+        <f aca="false">IF($I$5=1,M64,M77)</f>
+        <v>0.103818082762098</v>
+      </c>
+      <c r="N51" s="39" t="n">
+        <f aca="false">IF($I$5=1,N64,N77)</f>
+        <v>0.22271410640658</v>
+      </c>
+      <c r="O51" s="39" t="n">
+        <f aca="false">IF($I$5=1,O64,O77)</f>
+        <v>0.0570952049878576</v>
+      </c>
+      <c r="P51" s="39" t="n">
+        <f aca="false">IF($I$5=1,P64,P77)</f>
+        <v>-0.0148859501712823</v>
+      </c>
+      <c r="Q51" s="40" t="n">
         <f aca="false">SUM(I51:P51)</f>
         <v>1</v>
       </c>
+      <c r="R51" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*3/8</f>
+        <v>0.0712953433009536</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H52" s="25" t="n">
+      <c r="H52" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="31" t="n">
-        <v>0.355708</v>
-      </c>
-      <c r="J52" s="31" t="n">
-        <v>0.053393</v>
-      </c>
-      <c r="K52" s="31" t="n">
-        <v>0.225787</v>
-      </c>
-      <c r="L52" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="31" t="n">
-        <v>0.067296</v>
-      </c>
-      <c r="N52" s="31" t="n">
-        <v>0.140828</v>
-      </c>
-      <c r="O52" s="31" t="n">
-        <v>0.066225</v>
-      </c>
-      <c r="P52" s="31" t="n">
-        <v>0.090762</v>
-      </c>
-      <c r="Q52" s="32" t="n">
+      <c r="I52" s="39" t="n">
+        <f aca="false">IF($I$5=1,I65,I78)</f>
+        <v>0.51233747243856</v>
+      </c>
+      <c r="J52" s="39" t="n">
+        <f aca="false">IF($I$5=1,J65,J78)</f>
+        <v>-0.0515149800861837</v>
+      </c>
+      <c r="K52" s="39" t="n">
+        <f aca="false">IF($I$5=1,K65,K78)</f>
+        <v>0.289049004846895</v>
+      </c>
+      <c r="L52" s="39" t="n">
+        <f aca="false">IF($I$5=1,L65,L78)</f>
+        <v>-0.118237588349846</v>
+      </c>
+      <c r="M52" s="39" t="n">
+        <f aca="false">IF($I$5=1,M65,M78)</f>
+        <v>0.104794776991119</v>
+      </c>
+      <c r="N52" s="39" t="n">
+        <f aca="false">IF($I$5=1,N65,N78)</f>
+        <v>0.224975272003637</v>
+      </c>
+      <c r="O52" s="39" t="n">
+        <f aca="false">IF($I$5=1,O65,O78)</f>
+        <v>0.0567053212126911</v>
+      </c>
+      <c r="P52" s="39" t="n">
+        <f aca="false">IF($I$5=1,P65,P78)</f>
+        <v>-0.0181092790568729</v>
+      </c>
+      <c r="Q52" s="40" t="n">
         <f aca="false">SUM(I52:P52)</f>
-        <v>0.999999</v>
+        <v>1</v>
+      </c>
+      <c r="R52" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*4/8</f>
+        <v>0.0733937910679382</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H53" s="25" t="n">
+      <c r="H53" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="I53" s="31" t="n">
-        <v>0.395235</v>
-      </c>
-      <c r="J53" s="31" t="n">
-        <v>0.012603</v>
-      </c>
-      <c r="K53" s="31" t="n">
-        <v>0.241805</v>
-      </c>
-      <c r="L53" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="31" t="n">
-        <v>0.077326</v>
-      </c>
-      <c r="N53" s="31" t="n">
-        <v>0.165713</v>
-      </c>
-      <c r="O53" s="31" t="n">
-        <v>0.058845</v>
-      </c>
-      <c r="P53" s="31" t="n">
-        <v>0.048474</v>
-      </c>
-      <c r="Q53" s="32" t="n">
+      <c r="I53" s="39" t="n">
+        <f aca="false">IF($I$5=1,I66,I79)</f>
+        <v>0.516347959248806</v>
+      </c>
+      <c r="J53" s="39" t="n">
+        <f aca="false">IF($I$5=1,J66,J79)</f>
+        <v>-0.0546209546949111</v>
+      </c>
+      <c r="K53" s="39" t="n">
+        <f aca="false">IF($I$5=1,K66,K79)</f>
+        <v>0.290670830546466</v>
+      </c>
+      <c r="L53" s="39" t="n">
+        <f aca="false">IF($I$5=1,L66,L79)</f>
+        <v>-0.120388573416255</v>
+      </c>
+      <c r="M53" s="39" t="n">
+        <f aca="false">IF($I$5=1,M66,M79)</f>
+        <v>0.105771471220139</v>
+      </c>
+      <c r="N53" s="39" t="n">
+        <f aca="false">IF($I$5=1,N66,N79)</f>
+        <v>0.227236437600694</v>
+      </c>
+      <c r="O53" s="39" t="n">
+        <f aca="false">IF($I$5=1,O66,O79)</f>
+        <v>0.0563154374375245</v>
+      </c>
+      <c r="P53" s="39" t="n">
+        <f aca="false">IF($I$5=1,P66,P79)</f>
+        <v>-0.0213326079424636</v>
+      </c>
+      <c r="Q53" s="40" t="n">
         <f aca="false">SUM(I53:P53)</f>
-        <v>1.000001</v>
+        <v>1</v>
+      </c>
+      <c r="R53" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*5/8</f>
+        <v>0.0754922388349227</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H54" s="25" t="n">
+      <c r="H54" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="I54" s="31" t="n">
-        <v>0.420413</v>
-      </c>
-      <c r="J54" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="31" t="n">
-        <v>0.243156</v>
-      </c>
-      <c r="L54" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="31" t="n">
-        <v>0.096403</v>
-      </c>
-      <c r="N54" s="31" t="n">
-        <v>0.216029</v>
-      </c>
-      <c r="O54" s="31" t="n">
-        <v>0.023999</v>
-      </c>
-      <c r="P54" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="32" t="n">
+      <c r="I54" s="39" t="n">
+        <f aca="false">IF($I$5=1,I67,I80)</f>
+        <v>0.520358446059052</v>
+      </c>
+      <c r="J54" s="39" t="n">
+        <f aca="false">IF($I$5=1,J67,J80)</f>
+        <v>-0.0577269293036384</v>
+      </c>
+      <c r="K54" s="39" t="n">
+        <f aca="false">IF($I$5=1,K67,K80)</f>
+        <v>0.292292656246036</v>
+      </c>
+      <c r="L54" s="39" t="n">
+        <f aca="false">IF($I$5=1,L67,L80)</f>
+        <v>-0.122539558482664</v>
+      </c>
+      <c r="M54" s="39" t="n">
+        <f aca="false">IF($I$5=1,M67,M80)</f>
+        <v>0.10674816544916</v>
+      </c>
+      <c r="N54" s="39" t="n">
+        <f aca="false">IF($I$5=1,N67,N80)</f>
+        <v>0.229497603197751</v>
+      </c>
+      <c r="O54" s="39" t="n">
+        <f aca="false">IF($I$5=1,O67,O80)</f>
+        <v>0.055925553662358</v>
+      </c>
+      <c r="P54" s="39" t="n">
+        <f aca="false">IF($I$5=1,P67,P80)</f>
+        <v>-0.0245559368280542</v>
+      </c>
+      <c r="Q54" s="40" t="n">
         <f aca="false">SUM(I54:P54)</f>
         <v>1</v>
       </c>
+      <c r="R54" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*6/8</f>
+        <v>0.0775906866019072</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H55" s="25" t="n">
+      <c r="H55" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="I55" s="31" t="n">
-        <v>0.346988</v>
-      </c>
-      <c r="J55" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="31" t="n">
-        <v>0.036684</v>
-      </c>
-      <c r="L55" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="31" t="n">
-        <v>0.15095</v>
-      </c>
-      <c r="N55" s="31" t="n">
-        <v>0.465377</v>
-      </c>
-      <c r="O55" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="32" t="n">
+      <c r="I55" s="39" t="n">
+        <f aca="false">IF($I$5=1,I68,I81)</f>
+        <v>0.524368932869297</v>
+      </c>
+      <c r="J55" s="39" t="n">
+        <f aca="false">IF($I$5=1,J68,J81)</f>
+        <v>-0.0608329039123656</v>
+      </c>
+      <c r="K55" s="39" t="n">
+        <f aca="false">IF($I$5=1,K68,K81)</f>
+        <v>0.293914481945607</v>
+      </c>
+      <c r="L55" s="39" t="n">
+        <f aca="false">IF($I$5=1,L68,L81)</f>
+        <v>-0.124690543549074</v>
+      </c>
+      <c r="M55" s="39" t="n">
+        <f aca="false">IF($I$5=1,M68,M81)</f>
+        <v>0.10772485967818</v>
+      </c>
+      <c r="N55" s="39" t="n">
+        <f aca="false">IF($I$5=1,N68,N81)</f>
+        <v>0.231758768794809</v>
+      </c>
+      <c r="O55" s="39" t="n">
+        <f aca="false">IF($I$5=1,O68,O81)</f>
+        <v>0.0555356698871915</v>
+      </c>
+      <c r="P55" s="39" t="n">
+        <f aca="false">IF($I$5=1,P68,P81)</f>
+        <v>-0.0277792657136448</v>
+      </c>
+      <c r="Q55" s="40" t="n">
         <f aca="false">SUM(I55:P55)</f>
-        <v>0.999999</v>
+        <v>1</v>
+      </c>
+      <c r="R55" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*7/8</f>
+        <v>0.0796891343688918</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H56" s="25" t="n">
+      <c r="H56" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="I56" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="32" t="n">
+      <c r="I56" s="39" t="n">
+        <f aca="false">IF($I$5=1,I69,I82)</f>
+        <v>0.528379419679543</v>
+      </c>
+      <c r="J56" s="39" t="n">
+        <f aca="false">IF($I$5=1,J69,J82)</f>
+        <v>-0.0639388785210929</v>
+      </c>
+      <c r="K56" s="39" t="n">
+        <f aca="false">IF($I$5=1,K69,K82)</f>
+        <v>0.295536307645177</v>
+      </c>
+      <c r="L56" s="39" t="n">
+        <f aca="false">IF($I$5=1,L69,L82)</f>
+        <v>-0.126841528615483</v>
+      </c>
+      <c r="M56" s="39" t="n">
+        <f aca="false">IF($I$5=1,M69,M82)</f>
+        <v>0.108701553907201</v>
+      </c>
+      <c r="N56" s="39" t="n">
+        <f aca="false">IF($I$5=1,N69,N82)</f>
+        <v>0.234019934391866</v>
+      </c>
+      <c r="O56" s="39" t="n">
+        <f aca="false">IF($I$5=1,O69,O82)</f>
+        <v>0.055145786112025</v>
+      </c>
+      <c r="P56" s="39" t="n">
+        <f aca="false">IF($I$5=1,P69,P82)</f>
+        <v>-0.0310025945992354</v>
+      </c>
+      <c r="Q56" s="40" t="n">
         <f aca="false">SUM(I56:P56)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H58" s="28" t="s">
-        <v>39</v>
+      <c r="R56" s="40" t="n">
+        <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*8/8</f>
+        <v>0.0817875821358763</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H59" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>43</v>
+      <c r="H59" s="36" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H60" s="8" t="n">
+      <c r="H60" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="I60" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="K60" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="O60" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="P60" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R60" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$E$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.496295525197577</v>
+      </c>
+      <c r="J61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$F$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0390910816512745</v>
+      </c>
+      <c r="K61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$G$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.282561702048613</v>
+      </c>
+      <c r="L61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$H$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.109633648084208</v>
+      </c>
+      <c r="M61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$I$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.100888000075036</v>
+      </c>
+      <c r="N61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$J$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.215930609615409</v>
+      </c>
+      <c r="O61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$K$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.0582648563133571</v>
+      </c>
+      <c r="P61" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R61)*Matriz!$L$53+(Matriz!$E$56*$R61-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.00521596351451034</v>
+      </c>
+      <c r="Q61" s="40" t="n">
+        <f aca="false">SUM(I61:P61)</f>
+        <v>1</v>
+      </c>
+      <c r="R61" s="40" t="n">
+        <f aca="false">R48</f>
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H62" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$E$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.500306012007823</v>
+      </c>
+      <c r="J62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$F$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0421970562600018</v>
+      </c>
+      <c r="K62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$G$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.284183527748183</v>
+      </c>
+      <c r="L62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$H$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.111784633150617</v>
+      </c>
+      <c r="M62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$I$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.101864694304057</v>
+      </c>
+      <c r="N62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$J$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.218191775212466</v>
+      </c>
+      <c r="O62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$K$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.0578749725381906</v>
+      </c>
+      <c r="P62" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R62)*Matriz!$L$53+(Matriz!$E$56*$R62-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.00843929240010092</v>
+      </c>
+      <c r="Q62" s="40" t="n">
+        <f aca="false">SUM(I62:P62)</f>
+        <v>1</v>
+      </c>
+      <c r="R62" s="40" t="n">
+        <f aca="false">R49</f>
+        <v>0.0670984477669845</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H63" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$E$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.504316498818069</v>
+      </c>
+      <c r="J63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$F$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0453030308687291</v>
+      </c>
+      <c r="K63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$G$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.285805353447754</v>
+      </c>
+      <c r="L63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$H$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.113935618217027</v>
+      </c>
+      <c r="M63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$I$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.102841388533077</v>
+      </c>
+      <c r="N63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$J$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.220452940809523</v>
+      </c>
+      <c r="O63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$K$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.0574850887630241</v>
+      </c>
+      <c r="P63" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R63)*Matriz!$L$53+(Matriz!$E$56*$R63-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.0116626212856916</v>
+      </c>
+      <c r="Q63" s="40" t="n">
+        <f aca="false">SUM(I63:P63)</f>
+        <v>1</v>
+      </c>
+      <c r="R63" s="40" t="n">
+        <f aca="false">R50</f>
+        <v>0.0691968955339691</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H64" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$E$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.508326985628314</v>
+      </c>
+      <c r="J64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$F$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0484090054774564</v>
+      </c>
+      <c r="K64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$G$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.287427179147325</v>
+      </c>
+      <c r="L64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$H$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.116086603283436</v>
+      </c>
+      <c r="M64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$I$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.103818082762098</v>
+      </c>
+      <c r="N64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$J$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.22271410640658</v>
+      </c>
+      <c r="O64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$K$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.0570952049878576</v>
+      </c>
+      <c r="P64" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R64)*Matriz!$L$53+(Matriz!$E$56*$R64-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.0148859501712823</v>
+      </c>
+      <c r="Q64" s="40" t="n">
+        <f aca="false">SUM(I64:P64)</f>
+        <v>1</v>
+      </c>
+      <c r="R64" s="40" t="n">
+        <f aca="false">R51</f>
+        <v>0.0712953433009536</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H65" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$E$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.51233747243856</v>
+      </c>
+      <c r="J65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$F$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0515149800861837</v>
+      </c>
+      <c r="K65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$G$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.289049004846895</v>
+      </c>
+      <c r="L65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$H$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.118237588349846</v>
+      </c>
+      <c r="M65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$I$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.104794776991119</v>
+      </c>
+      <c r="N65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$J$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.224975272003637</v>
+      </c>
+      <c r="O65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$K$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.0567053212126911</v>
+      </c>
+      <c r="P65" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R65)*Matriz!$L$53+(Matriz!$E$56*$R65-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.0181092790568729</v>
+      </c>
+      <c r="Q65" s="40" t="n">
+        <f aca="false">SUM(I65:P65)</f>
+        <v>1</v>
+      </c>
+      <c r="R65" s="40" t="n">
+        <f aca="false">R52</f>
+        <v>0.0733937910679382</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$E$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.516347959248806</v>
+      </c>
+      <c r="J66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$F$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0546209546949111</v>
+      </c>
+      <c r="K66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$G$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.290670830546466</v>
+      </c>
+      <c r="L66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$H$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.120388573416255</v>
+      </c>
+      <c r="M66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$I$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.105771471220139</v>
+      </c>
+      <c r="N66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$J$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.227236437600694</v>
+      </c>
+      <c r="O66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$K$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.0563154374375245</v>
+      </c>
+      <c r="P66" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R66)*Matriz!$L$53+(Matriz!$E$56*$R66-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.0213326079424636</v>
+      </c>
+      <c r="Q66" s="40" t="n">
+        <f aca="false">SUM(I66:P66)</f>
+        <v>1</v>
+      </c>
+      <c r="R66" s="40" t="n">
+        <f aca="false">R53</f>
+        <v>0.0754922388349227</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H67" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="I67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$E$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.520358446059052</v>
+      </c>
+      <c r="J67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$F$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0577269293036384</v>
+      </c>
+      <c r="K67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$G$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.292292656246036</v>
+      </c>
+      <c r="L67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$H$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.122539558482664</v>
+      </c>
+      <c r="M67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$I$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.10674816544916</v>
+      </c>
+      <c r="N67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$J$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.229497603197751</v>
+      </c>
+      <c r="O67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$K$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.055925553662358</v>
+      </c>
+      <c r="P67" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R67)*Matriz!$L$53+(Matriz!$E$56*$R67-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.0245559368280542</v>
+      </c>
+      <c r="Q67" s="40" t="n">
+        <f aca="false">SUM(I67:P67)</f>
+        <v>1</v>
+      </c>
+      <c r="R67" s="40" t="n">
+        <f aca="false">R54</f>
+        <v>0.0775906866019072</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H68" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$E$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.524368932869297</v>
+      </c>
+      <c r="J68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$F$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0608329039123656</v>
+      </c>
+      <c r="K68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$G$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.293914481945607</v>
+      </c>
+      <c r="L68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$H$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.124690543549074</v>
+      </c>
+      <c r="M68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$I$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.10772485967818</v>
+      </c>
+      <c r="N68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$J$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.231758768794809</v>
+      </c>
+      <c r="O68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$K$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.0555356698871915</v>
+      </c>
+      <c r="P68" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R68)*Matriz!$L$53+(Matriz!$E$56*$R68-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.0277792657136448</v>
+      </c>
+      <c r="Q68" s="40" t="n">
+        <f aca="false">SUM(I68:P68)</f>
+        <v>1</v>
+      </c>
+      <c r="R68" s="40" t="n">
+        <f aca="false">R55</f>
+        <v>0.0796891343688918</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H69" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="I69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$E$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$E$54)/Matriz!$E$59</f>
+        <v>0.528379419679543</v>
+      </c>
+      <c r="J69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$F$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$F$54)/Matriz!$E$59</f>
+        <v>-0.0639388785210929</v>
+      </c>
+      <c r="K69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$G$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$G$54)/Matriz!$E$59</f>
+        <v>0.295536307645177</v>
+      </c>
+      <c r="L69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$H$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$H$54)/Matriz!$E$59</f>
+        <v>-0.126841528615483</v>
+      </c>
+      <c r="M69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$I$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$I$54)/Matriz!$E$59</f>
+        <v>0.108701553907201</v>
+      </c>
+      <c r="N69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$J$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$J$54)/Matriz!$E$59</f>
+        <v>0.234019934391866</v>
+      </c>
+      <c r="O69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$K$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$K$54)/Matriz!$E$59</f>
+        <v>0.055145786112025</v>
+      </c>
+      <c r="P69" s="39" t="n">
+        <f aca="false">((Matriz!$E$58-Matriz!$E$57*$R69)*Matriz!$L$53+(Matriz!$E$56*$R69-Matriz!$E$57)*Matriz!$L$54)/Matriz!$E$59</f>
+        <v>-0.0310025945992354</v>
+      </c>
+      <c r="Q69" s="40" t="n">
+        <f aca="false">SUM(I69:P69)</f>
+        <v>1</v>
+      </c>
+      <c r="R69" s="40" t="n">
+        <f aca="false">R56</f>
+        <v>0.0817875821358763</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H72" s="36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H73" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="I73" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="K73" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="L73" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="M73" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="N73" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="O73" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="P73" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q73" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R73" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="41" t="n">
+        <v>0.284777</v>
+      </c>
+      <c r="J74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="41" t="n">
+        <v>0.159932</v>
+      </c>
+      <c r="N74" s="41" t="n">
+        <v>0.555291</v>
+      </c>
+      <c r="O74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="40" t="n">
+        <f aca="false">SUM(I74:P74)</f>
+        <v>1</v>
+      </c>
+      <c r="R74" s="42" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H75" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" s="41" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="J75" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="41" t="n">
+        <v>0.160506</v>
+      </c>
+      <c r="N75" s="41" t="n">
+        <v>0.601094</v>
+      </c>
+      <c r="O75" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="40" t="n">
+        <f aca="false">SUM(I75:P75)</f>
+        <v>1</v>
+      </c>
+      <c r="R75" s="42" t="n">
+        <v>0.067098</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H76" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I76" s="41" t="n">
+        <v>0.192024</v>
+      </c>
+      <c r="J76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="41" t="n">
+        <v>0.161079</v>
+      </c>
+      <c r="N76" s="41" t="n">
+        <v>0.646897</v>
+      </c>
+      <c r="O76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="40" t="n">
+        <f aca="false">SUM(I76:P76)</f>
+        <v>1</v>
+      </c>
+      <c r="R76" s="42" t="n">
+        <v>0.069197</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H77" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I77" s="41" t="n">
+        <v>0.145647</v>
+      </c>
+      <c r="J77" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="41" t="n">
+        <v>0.161653</v>
+      </c>
+      <c r="N77" s="41" t="n">
+        <v>0.6927</v>
+      </c>
+      <c r="O77" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="40" t="n">
+        <f aca="false">SUM(I77:P77)</f>
+        <v>1</v>
+      </c>
+      <c r="R77" s="42" t="n">
+        <v>0.071295</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H78" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" s="41" t="n">
+        <v>0.09927</v>
+      </c>
+      <c r="J78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="41" t="n">
+        <v>0.162226</v>
+      </c>
+      <c r="N78" s="41" t="n">
+        <v>0.738503</v>
+      </c>
+      <c r="O78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="40" t="n">
+        <f aca="false">SUM(I78:P78)</f>
+        <v>0.999999</v>
+      </c>
+      <c r="R78" s="42" t="n">
+        <v>0.073394</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H79" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I79" s="41" t="n">
+        <v>0.052894</v>
+      </c>
+      <c r="J79" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="41" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="N79" s="41" t="n">
+        <v>0.784306</v>
+      </c>
+      <c r="O79" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="40" t="n">
+        <f aca="false">SUM(I79:P79)</f>
+        <v>1</v>
+      </c>
+      <c r="R79" s="42" t="n">
+        <v>0.075492</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="I80" s="41" t="n">
+        <v>0.006517</v>
+      </c>
+      <c r="J80" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="41" t="n">
+        <v>0.163374</v>
+      </c>
+      <c r="N80" s="41" t="n">
+        <v>0.830109</v>
+      </c>
+      <c r="O80" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="40" t="n">
+        <f aca="false">SUM(I80:P80)</f>
+        <v>1</v>
+      </c>
+      <c r="R80" s="42" t="n">
+        <v>0.077591</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H81" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I81" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="41" t="n">
+        <v>0.087903</v>
+      </c>
+      <c r="N81" s="41" t="n">
+        <v>0.912097</v>
+      </c>
+      <c r="O81" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="40" t="n">
+        <f aca="false">SUM(I81:P81)</f>
+        <v>1</v>
+      </c>
+      <c r="R81" s="42" t="n">
+        <v>0.079689</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H82" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="I82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="40" t="n">
+        <f aca="false">SUM(I82:P82)</f>
+        <v>1</v>
+      </c>
+      <c r="R82" s="42" t="n">
+        <v>0.081788</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H86" s="36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H87" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I87" s="8" t="n">
+        <f aca="false">STDEV(RENDIMIENTOS!$J$3:$J$251)</f>
+        <v>0.0106681513686276</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H89" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H90" s="8" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="I60" s="33" t="n">
+      <c r="I90" s="23" t="n">
         <f aca="false">$I$14</f>
-        <v>0.07</v>
-      </c>
-      <c r="J60" s="34" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="K90" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="8" t="n">
+        <f aca="false">K90*$I$87</f>
+        <v>0</v>
+      </c>
+      <c r="M90" s="23" t="n">
+        <f aca="false">$I$14+K90*($I$4-$I$14)</f>
+        <v>0.065</v>
+      </c>
+      <c r="N90" s="8" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="K60" s="33" t="n">
-        <f aca="false">$I$14</f>
-        <v>0.07</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H61" s="8" t="n">
+      <c r="O90" s="23" t="n">
+        <f aca="false">MAX($J$19:$J$27)</f>
+        <v>0.0817875821358763</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H91" s="8" t="n">
         <f aca="false">$I$12</f>
-        <v>0.0172079118776168</v>
-      </c>
-      <c r="I61" s="33" t="n">
+        <v>0.0122217948332109</v>
+      </c>
+      <c r="I91" s="23" t="n">
         <f aca="false">$I$7</f>
         <v>0.0817875821358763</v>
       </c>
-      <c r="J61" s="34" t="n">
-        <f aca="false">1</f>
+      <c r="K91" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K61" s="33" t="n">
-        <f aca="false">$I$4</f>
+      <c r="L91" s="8" t="n">
+        <f aca="false">K91*$I$87</f>
+        <v>0.0106681513686276</v>
+      </c>
+      <c r="M91" s="23" t="n">
+        <f aca="false">$I$14+K91*($I$4-$I$14)</f>
         <v>0.0668941515629918</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H62" s="8" t="n">
-        <f aca="false">1.6*$I$12</f>
-        <v>0.0275326590041868</v>
-      </c>
-      <c r="I62" s="33" t="n">
-        <f aca="false">$I$14+1.6*($I$7-$I$14)</f>
-        <v>0.0888601314174021</v>
-      </c>
-      <c r="J62" s="34" t="n">
-        <f aca="false">2</f>
-        <v>2</v>
-      </c>
-      <c r="K62" s="33" t="n">
-        <f aca="false">$I$14+2*($I$4-$I$14)</f>
-        <v>0.0637883031259836</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H65" s="28" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H67" s="35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H68" s="35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H69" s="35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H70" s="35" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H71" s="35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H72" s="35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H73" s="35" t="s">
-        <v>52</v>
+      <c r="N91" s="8" t="n">
+        <f aca="false">MAX($I$19:$I$27)</f>
+        <v>0.0122217948332109</v>
+      </c>
+      <c r="O91" s="23" t="n">
+        <f aca="false">MAX($J$19:$J$27)</f>
+        <v>0.0817875821358763</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H92" s="8" t="n">
+        <f aca="false">1.5*$I$12</f>
+        <v>0.0183326922498164</v>
+      </c>
+      <c r="I92" s="23" t="n">
+        <f aca="false">$I$14+1.5*($I$7-$I$14)</f>
+        <v>0.0901813732038144</v>
+      </c>
+      <c r="K92" s="43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L92" s="8" t="n">
+        <f aca="false">K92*$I$87</f>
+        <v>0.0160022270529414</v>
+      </c>
+      <c r="M92" s="23" t="n">
+        <f aca="false">$I$14+K92*($I$4-$I$14)</f>
+        <v>0.0678412273444877</v>
+      </c>
+      <c r="N92" s="8" t="n">
+        <f aca="false">MAX($I$19:$I$27)</f>
+        <v>0.0122217948332109</v>
+      </c>
+      <c r="O92" s="23" t="n">
+        <f aca="false">$I$14</f>
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H95" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H96" s="44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H97" s="44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H98" s="44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H99" s="44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H100" s="44" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H101" s="44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H102" s="44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H103" s="44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H104" s="44" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H105" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H106" s="44" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H107" s="44" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Markowits/Portafolio_Markowitz_Profesor.xlsx
+++ b/Markowits/Portafolio_Markowitz_Profesor.xlsx
@@ -846,10 +846,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0122217948332109</c:v>
+                  <c:v>0.0172079118776168</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0122217948332109</c:v>
+                  <c:v>0.0172079118776168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1096,10 +1096,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0122217948332109</c:v>
+                  <c:v>0.0172079118776168</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0183326922498164</c:v>
+                  <c:v>0.0258118678164251</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1117,7 +1117,7 @@
                   <c:v>0.0817875821358763</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0901813732038144</c:v>
+                  <c:v>0.0901813732038145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1379,31 +1379,31 @@
                 <c:formatCode>0.00000000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.0117644715517125</c:v>
+                  <c:v>0.0134292362819857</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0118200679176229</c:v>
+                  <c:v>0.0137603941110514</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0118761254022205</c:v>
+                  <c:v>0.0141262010297019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0119326375067375</c:v>
+                  <c:v>0.0145240464794026</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0119895978027211</c:v>
+                  <c:v>0.0149513580978967</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0120469999327929</c:v>
+                  <c:v>0.0154057133789584</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0121048376113144</c:v>
+                  <c:v>0.0158847678278917</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0121631046249613</c:v>
+                  <c:v>0.0164528228463165</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0122217948332109</c:v>
+                  <c:v>0.0172079118776168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1415,28 +1415,28 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.065</c:v>
+                  <c:v>0.0649999951295349</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0670984477669845</c:v>
+                  <c:v>0.0670984488211228</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.069196895533969</c:v>
+                  <c:v>0.0691968808417637</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0712953433009536</c:v>
+                  <c:v>0.0712953345333515</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0733937910679381</c:v>
+                  <c:v>0.0733937303095967</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0754922388349227</c:v>
+                  <c:v>0.0754922202455803</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0775906866019072</c:v>
+                  <c:v>0.0775906739371681</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0796891343688918</c:v>
+                  <c:v>0.0796891406688979</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.0817875821358763</c:v>
@@ -1446,11 +1446,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="31193797"/>
-        <c:axId val="78387778"/>
+        <c:axId val="8799847"/>
+        <c:axId val="96165564"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="31193797"/>
+        <c:axId val="8799847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1516,12 +1516,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78387778"/>
+        <c:crossAx val="96165564"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="78387778"/>
+        <c:axId val="96165564"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.06"/>
@@ -1588,7 +1588,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31193797"/>
+        <c:crossAx val="8799847"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -21828,7 +21828,7 @@
         <v>27</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="25" t="s">
         <v>28</v>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="D7" s="26" t="n">
         <f aca="false">INDEX(I$48:I$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>0.528379419679543</v>
+        <v>0</v>
       </c>
       <c r="E7" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$B$3:$B$251)*$I$3</f>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="D8" s="26" t="n">
         <f aca="false">INDEX(J$48:J$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>-0.0639388785210929</v>
+        <v>0</v>
       </c>
       <c r="E8" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$C$3:$C$251)*$I$3</f>
@@ -21895,7 +21895,7 @@
       </c>
       <c r="D9" s="26" t="n">
         <f aca="false">INDEX(K$48:K$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>0.295536307645177</v>
+        <v>0</v>
       </c>
       <c r="E9" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$D$3:$D$251)*$I$3</f>
@@ -21910,7 +21910,7 @@
       </c>
       <c r="I9" s="27" t="n">
         <f aca="false">SUMPRODUCT(MMULT(Matriz!$E$31:$L$38,D7:D14),D7:D14)</f>
-        <v>0.000149372268945101</v>
+        <v>0.000296112231187824</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="D10" s="26" t="n">
         <f aca="false">INDEX(L$48:L$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>-0.126841528615483</v>
+        <v>0</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$E$3:$E$251)*$I$3</f>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="D11" s="26" t="n">
         <f aca="false">INDEX(M$48:M$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>0.108701553907201</v>
+        <v>0</v>
       </c>
       <c r="E11" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$F$3:$F$251)*$I$3</f>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="D12" s="26" t="n">
         <f aca="false">INDEX(N$48:N$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>0.234019934391866</v>
+        <v>1</v>
       </c>
       <c r="E12" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$G$3:$G$251)*$I$3</f>
@@ -21968,7 +21968,7 @@
       </c>
       <c r="I12" s="8" t="n">
         <f aca="false">SQRT(I9)</f>
-        <v>0.0122217948332109</v>
+        <v>0.0172079118776168</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="D13" s="26" t="n">
         <f aca="false">INDEX(O$48:O$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>0.055145786112025</v>
+        <v>0</v>
       </c>
       <c r="E13" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$H$3:$H$251)*$I$3</f>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="D14" s="26" t="n">
         <f aca="false">INDEX(P$48:P$56,MATCH(MAX($K$19:$K$27),$K$19:$K$27,0))</f>
-        <v>-0.0310025945992354</v>
+        <v>0</v>
       </c>
       <c r="E14" s="23" t="n">
         <f aca="false">AVERAGE(RENDIMIENTOS!$I$3:$I$251)*$I$3</f>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="F15" s="31" t="n">
         <f aca="false">SUMPRODUCT(D7:D14,F7:F14)</f>
-        <v>0.894254951070821</v>
+        <v>1.14498888583895</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="I16" s="9" t="n">
         <f aca="false">+(I7-I14)/I12</f>
-        <v>1.37357747900157</v>
+        <v>0.975573460351852</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22065,19 +22065,19 @@
       </c>
       <c r="I19" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I48:$P48,Matriz!$E$31:$L$38),$I48:$P48))</f>
-        <v>0.0117644715517125</v>
+        <v>0.0134292362819857</v>
       </c>
       <c r="J19" s="35" t="n">
         <f aca="false">SUMPRODUCT($I48:$P48,$I$46:$P$46)</f>
-        <v>0.065</v>
+        <v>0.0649999951295349</v>
       </c>
       <c r="K19" s="9" t="n">
         <f aca="false">(J19-$I$14)/I19</f>
-        <v>0</v>
+        <v>-3.62676254425688E-007</v>
       </c>
       <c r="L19" s="9" t="n">
         <f aca="false">SUMPRODUCT($I48:$P48,$I$47:$P$47)</f>
-        <v>0.873442556027565</v>
+        <v>1.04813704749361</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22086,19 +22086,19 @@
       </c>
       <c r="I20" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I49:$P49,Matriz!$E$31:$L$38),$I49:$P49))</f>
-        <v>0.0118200679176229</v>
+        <v>0.0137603941110514</v>
       </c>
       <c r="J20" s="35" t="n">
         <f aca="false">SUMPRODUCT($I49:$P49,$I$46:$P$46)</f>
-        <v>0.0670984477669845</v>
+        <v>0.0670984488211228</v>
       </c>
       <c r="K20" s="9" t="n">
         <f aca="false">(J20-$I$14)/I20</f>
-        <v>0.1775326319281</v>
+        <v>0.152499180196985</v>
       </c>
       <c r="L20" s="9" t="n">
         <f aca="false">SUMPRODUCT($I49:$P49,$I$47:$P$47)</f>
-        <v>0.876044105407972</v>
+        <v>1.06773643315597</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22107,19 +22107,19 @@
       </c>
       <c r="I21" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I50:$P50,Matriz!$E$31:$L$38),$I50:$P50))</f>
-        <v>0.0118761254022205</v>
+        <v>0.0141262010297019</v>
       </c>
       <c r="J21" s="35" t="n">
         <f aca="false">SUMPRODUCT($I50:$P50,$I$46:$P$46)</f>
-        <v>0.069196895533969</v>
+        <v>0.0691968808417637</v>
       </c>
       <c r="K21" s="9" t="n">
         <f aca="false">(J21-$I$14)/I21</f>
-        <v>0.35338929085275</v>
+        <v>0.297099045450313</v>
       </c>
       <c r="L21" s="9" t="n">
         <f aca="false">SUMPRODUCT($I50:$P50,$I$47:$P$47)</f>
-        <v>0.878645654788379</v>
+        <v>1.08733525423208</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22128,19 +22128,19 @@
       </c>
       <c r="I22" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I51:$P51,Matriz!$E$31:$L$38),$I51:$P51))</f>
-        <v>0.0119326375067375</v>
+        <v>0.0145240464794026</v>
       </c>
       <c r="J22" s="35" t="n">
         <f aca="false">SUMPRODUCT($I51:$P51,$I$46:$P$46)</f>
-        <v>0.0712953433009536</v>
+        <v>0.0712953345333515</v>
       </c>
       <c r="K22" s="9" t="n">
         <f aca="false">(J22-$I$14)/I22</f>
-        <v>0.527573497259014</v>
+        <v>0.433442191353441</v>
       </c>
       <c r="L22" s="9" t="n">
         <f aca="false">SUMPRODUCT($I51:$P51,$I$47:$P$47)</f>
-        <v>0.881247204168786</v>
+        <v>1.10693463989443</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22149,19 +22149,19 @@
       </c>
       <c r="I23" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I52:$P52,Matriz!$E$31:$L$38),$I52:$P52))</f>
-        <v>0.0119895978027211</v>
+        <v>0.0149513580978967</v>
       </c>
       <c r="J23" s="35" t="n">
         <f aca="false">SUMPRODUCT($I52:$P52,$I$46:$P$46)</f>
-        <v>0.0733937910679381</v>
+        <v>0.0733937303095967</v>
       </c>
       <c r="K23" s="9" t="n">
         <f aca="false">(J23-$I$14)/I23</f>
-        <v>0.700089461385697</v>
+        <v>0.561402533110186</v>
       </c>
       <c r="L23" s="9" t="n">
         <f aca="false">SUMPRODUCT($I52:$P52,$I$47:$P$47)</f>
-        <v>0.883848753549193</v>
+        <v>1.12653273681246</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22170,19 +22170,19 @@
       </c>
       <c r="I24" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I53:$P53,Matriz!$E$31:$L$38),$I53:$P53))</f>
-        <v>0.0120469999327929</v>
+        <v>0.0154057133789584</v>
       </c>
       <c r="J24" s="35" t="n">
         <f aca="false">SUMPRODUCT($I53:$P53,$I$46:$P$46)</f>
-        <v>0.0754922388349227</v>
+        <v>0.0754922202455803</v>
       </c>
       <c r="K24" s="9" t="n">
         <f aca="false">(J24-$I$14)/I24</f>
-        <v>0.870942051419955</v>
+        <v>0.681060330507695</v>
       </c>
       <c r="L24" s="9" t="n">
         <f aca="false">SUMPRODUCT($I53:$P53,$I$47:$P$47)</f>
-        <v>0.8864503029296</v>
+        <v>1.14613284663289</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22191,19 +22191,19 @@
       </c>
       <c r="I25" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I54:$P54,Matriz!$E$31:$L$38),$I54:$P54))</f>
-        <v>0.0121048376113144</v>
+        <v>0.0158847678278917</v>
       </c>
       <c r="J25" s="35" t="n">
         <f aca="false">SUMPRODUCT($I54:$P54,$I$46:$P$46)</f>
-        <v>0.0775906866019072</v>
+        <v>0.0775906739371681</v>
       </c>
       <c r="K25" s="9" t="n">
         <f aca="false">(J25-$I$14)/I25</f>
-        <v>1.04013676235844</v>
+        <v>0.792625619309363</v>
       </c>
       <c r="L25" s="9" t="n">
         <f aca="false">SUMPRODUCT($I54:$P54,$I$47:$P$47)</f>
-        <v>0.889051852310007</v>
+        <v>1.16573223229525</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22212,19 +22212,19 @@
       </c>
       <c r="I26" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I55:$P55,Matriz!$E$31:$L$38),$I55:$P55))</f>
-        <v>0.0121631046249613</v>
+        <v>0.0164528228463165</v>
       </c>
       <c r="J26" s="35" t="n">
         <f aca="false">SUMPRODUCT($I55:$P55,$I$46:$P$46)</f>
-        <v>0.0796891343688918</v>
+        <v>0.0796891406688979</v>
       </c>
       <c r="K26" s="9" t="n">
         <f aca="false">(J26-$I$14)/I26</f>
-        <v>1.20767968555878</v>
+        <v>0.892803673029676</v>
       </c>
       <c r="L26" s="9" t="n">
         <f aca="false">SUMPRODUCT($I55:$P55,$I$47:$P$47)</f>
-        <v>0.891653401690414</v>
+        <v>1.15762542002814</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="I27" s="34" t="n">
         <f aca="false">SQRT(SUMPRODUCT(MMULT($I56:$P56,Matriz!$E$31:$L$38),$I56:$P56))</f>
-        <v>0.0122217948332109</v>
+        <v>0.0172079118776168</v>
       </c>
       <c r="J27" s="35" t="n">
         <f aca="false">SUMPRODUCT($I56:$P56,$I$46:$P$46)</f>
@@ -22241,11 +22241,11 @@
       </c>
       <c r="K27" s="9" t="n">
         <f aca="false">(J27-$I$14)/I27</f>
-        <v>1.37357747900157</v>
+        <v>0.975573460351852</v>
       </c>
       <c r="L27" s="9" t="n">
         <f aca="false">SUMPRODUCT($I56:$P56,$I$47:$P$47)</f>
-        <v>0.894254951070821</v>
+        <v>1.14498888583895</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22368,35 +22368,35 @@
       </c>
       <c r="I48" s="39" t="n">
         <f aca="false">IF($I$5=1,I61,I74)</f>
-        <v>0.496295525197577</v>
+        <v>0.284777</v>
       </c>
       <c r="J48" s="39" t="n">
         <f aca="false">IF($I$5=1,J61,J74)</f>
-        <v>-0.0390910816512745</v>
+        <v>0</v>
       </c>
       <c r="K48" s="39" t="n">
         <f aca="false">IF($I$5=1,K61,K74)</f>
-        <v>0.282561702048613</v>
+        <v>0</v>
       </c>
       <c r="L48" s="39" t="n">
         <f aca="false">IF($I$5=1,L61,L74)</f>
-        <v>-0.109633648084208</v>
+        <v>0</v>
       </c>
       <c r="M48" s="39" t="n">
         <f aca="false">IF($I$5=1,M61,M74)</f>
-        <v>0.100888000075036</v>
+        <v>0.159932</v>
       </c>
       <c r="N48" s="39" t="n">
         <f aca="false">IF($I$5=1,N61,N74)</f>
-        <v>0.215930609615409</v>
+        <v>0.555291</v>
       </c>
       <c r="O48" s="39" t="n">
         <f aca="false">IF($I$5=1,O61,O74)</f>
-        <v>0.0582648563133571</v>
+        <v>0</v>
       </c>
       <c r="P48" s="39" t="n">
         <f aca="false">IF($I$5=1,P61,P74)</f>
-        <v>-0.00521596351451034</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="40" t="n">
         <f aca="false">SUM(I48:P48)</f>
@@ -22413,35 +22413,35 @@
       </c>
       <c r="I49" s="39" t="n">
         <f aca="false">IF($I$5=1,I62,I75)</f>
-        <v>0.500306012007823</v>
+        <v>0.2384</v>
       </c>
       <c r="J49" s="39" t="n">
         <f aca="false">IF($I$5=1,J62,J75)</f>
-        <v>-0.0421970562600018</v>
+        <v>0</v>
       </c>
       <c r="K49" s="39" t="n">
         <f aca="false">IF($I$5=1,K62,K75)</f>
-        <v>0.284183527748183</v>
+        <v>0</v>
       </c>
       <c r="L49" s="39" t="n">
         <f aca="false">IF($I$5=1,L62,L75)</f>
-        <v>-0.111784633150617</v>
+        <v>0</v>
       </c>
       <c r="M49" s="39" t="n">
         <f aca="false">IF($I$5=1,M62,M75)</f>
-        <v>0.101864694304057</v>
+        <v>0.160506</v>
       </c>
       <c r="N49" s="39" t="n">
         <f aca="false">IF($I$5=1,N62,N75)</f>
-        <v>0.218191775212466</v>
+        <v>0.601094</v>
       </c>
       <c r="O49" s="39" t="n">
         <f aca="false">IF($I$5=1,O62,O75)</f>
-        <v>0.0578749725381906</v>
+        <v>0</v>
       </c>
       <c r="P49" s="39" t="n">
         <f aca="false">IF($I$5=1,P62,P75)</f>
-        <v>-0.00843929240010092</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="40" t="n">
         <f aca="false">SUM(I49:P49)</f>
@@ -22458,35 +22458,35 @@
       </c>
       <c r="I50" s="39" t="n">
         <f aca="false">IF($I$5=1,I63,I76)</f>
-        <v>0.504316498818069</v>
+        <v>0.192024</v>
       </c>
       <c r="J50" s="39" t="n">
         <f aca="false">IF($I$5=1,J63,J76)</f>
-        <v>-0.0453030308687291</v>
+        <v>0</v>
       </c>
       <c r="K50" s="39" t="n">
         <f aca="false">IF($I$5=1,K63,K76)</f>
-        <v>0.285805353447754</v>
+        <v>0</v>
       </c>
       <c r="L50" s="39" t="n">
         <f aca="false">IF($I$5=1,L63,L76)</f>
-        <v>-0.113935618217027</v>
+        <v>0</v>
       </c>
       <c r="M50" s="39" t="n">
         <f aca="false">IF($I$5=1,M63,M76)</f>
-        <v>0.102841388533077</v>
+        <v>0.161079</v>
       </c>
       <c r="N50" s="39" t="n">
         <f aca="false">IF($I$5=1,N63,N76)</f>
-        <v>0.220452940809523</v>
+        <v>0.646897</v>
       </c>
       <c r="O50" s="39" t="n">
         <f aca="false">IF($I$5=1,O63,O76)</f>
-        <v>0.0574850887630241</v>
+        <v>0</v>
       </c>
       <c r="P50" s="39" t="n">
         <f aca="false">IF($I$5=1,P63,P76)</f>
-        <v>-0.0116626212856916</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="40" t="n">
         <f aca="false">SUM(I50:P50)</f>
@@ -22503,35 +22503,35 @@
       </c>
       <c r="I51" s="39" t="n">
         <f aca="false">IF($I$5=1,I64,I77)</f>
-        <v>0.508326985628314</v>
+        <v>0.145647</v>
       </c>
       <c r="J51" s="39" t="n">
         <f aca="false">IF($I$5=1,J64,J77)</f>
-        <v>-0.0484090054774564</v>
+        <v>0</v>
       </c>
       <c r="K51" s="39" t="n">
         <f aca="false">IF($I$5=1,K64,K77)</f>
-        <v>0.287427179147325</v>
+        <v>0</v>
       </c>
       <c r="L51" s="39" t="n">
         <f aca="false">IF($I$5=1,L64,L77)</f>
-        <v>-0.116086603283436</v>
+        <v>0</v>
       </c>
       <c r="M51" s="39" t="n">
         <f aca="false">IF($I$5=1,M64,M77)</f>
-        <v>0.103818082762098</v>
+        <v>0.161653</v>
       </c>
       <c r="N51" s="39" t="n">
         <f aca="false">IF($I$5=1,N64,N77)</f>
-        <v>0.22271410640658</v>
+        <v>0.6927</v>
       </c>
       <c r="O51" s="39" t="n">
         <f aca="false">IF($I$5=1,O64,O77)</f>
-        <v>0.0570952049878576</v>
+        <v>0</v>
       </c>
       <c r="P51" s="39" t="n">
         <f aca="false">IF($I$5=1,P64,P77)</f>
-        <v>-0.0148859501712823</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="40" t="n">
         <f aca="false">SUM(I51:P51)</f>
@@ -22548,39 +22548,39 @@
       </c>
       <c r="I52" s="39" t="n">
         <f aca="false">IF($I$5=1,I65,I78)</f>
-        <v>0.51233747243856</v>
+        <v>0.09927</v>
       </c>
       <c r="J52" s="39" t="n">
         <f aca="false">IF($I$5=1,J65,J78)</f>
-        <v>-0.0515149800861837</v>
+        <v>0</v>
       </c>
       <c r="K52" s="39" t="n">
         <f aca="false">IF($I$5=1,K65,K78)</f>
-        <v>0.289049004846895</v>
+        <v>0</v>
       </c>
       <c r="L52" s="39" t="n">
         <f aca="false">IF($I$5=1,L65,L78)</f>
-        <v>-0.118237588349846</v>
+        <v>0</v>
       </c>
       <c r="M52" s="39" t="n">
         <f aca="false">IF($I$5=1,M65,M78)</f>
-        <v>0.104794776991119</v>
+        <v>0.162226</v>
       </c>
       <c r="N52" s="39" t="n">
         <f aca="false">IF($I$5=1,N65,N78)</f>
-        <v>0.224975272003637</v>
+        <v>0.738503</v>
       </c>
       <c r="O52" s="39" t="n">
         <f aca="false">IF($I$5=1,O65,O78)</f>
-        <v>0.0567053212126911</v>
+        <v>0</v>
       </c>
       <c r="P52" s="39" t="n">
         <f aca="false">IF($I$5=1,P65,P78)</f>
-        <v>-0.0181092790568729</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="40" t="n">
         <f aca="false">SUM(I52:P52)</f>
-        <v>1</v>
+        <v>0.999999</v>
       </c>
       <c r="R52" s="40" t="n">
         <f aca="false">$I$14+(MAX($E$7:$E$14)-$I$14)*4/8</f>
@@ -22593,35 +22593,35 @@
       </c>
       <c r="I53" s="39" t="n">
         <f aca="false">IF($I$5=1,I66,I79)</f>
-        <v>0.516347959248806</v>
+        <v>0.052894</v>
       </c>
       <c r="J53" s="39" t="n">
         <f aca="false">IF($I$5=1,J66,J79)</f>
-        <v>-0.0546209546949111</v>
+        <v>0</v>
       </c>
       <c r="K53" s="39" t="n">
         <f aca="false">IF($I$5=1,K66,K79)</f>
-        <v>0.290670830546466</v>
+        <v>0</v>
       </c>
       <c r="L53" s="39" t="n">
         <f aca="false">IF($I$5=1,L66,L79)</f>
-        <v>-0.120388573416255</v>
+        <v>0</v>
       </c>
       <c r="M53" s="39" t="n">
         <f aca="false">IF($I$5=1,M66,M79)</f>
-        <v>0.105771471220139</v>
+        <v>0.1628</v>
       </c>
       <c r="N53" s="39" t="n">
         <f aca="false">IF($I$5=1,N66,N79)</f>
-        <v>0.227236437600694</v>
+        <v>0.784306</v>
       </c>
       <c r="O53" s="39" t="n">
         <f aca="false">IF($I$5=1,O66,O79)</f>
-        <v>0.0563154374375245</v>
+        <v>0</v>
       </c>
       <c r="P53" s="39" t="n">
         <f aca="false">IF($I$5=1,P66,P79)</f>
-        <v>-0.0213326079424636</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="40" t="n">
         <f aca="false">SUM(I53:P53)</f>
@@ -22638,35 +22638,35 @@
       </c>
       <c r="I54" s="39" t="n">
         <f aca="false">IF($I$5=1,I67,I80)</f>
-        <v>0.520358446059052</v>
+        <v>0.006517</v>
       </c>
       <c r="J54" s="39" t="n">
         <f aca="false">IF($I$5=1,J67,J80)</f>
-        <v>-0.0577269293036384</v>
+        <v>0</v>
       </c>
       <c r="K54" s="39" t="n">
         <f aca="false">IF($I$5=1,K67,K80)</f>
-        <v>0.292292656246036</v>
+        <v>0</v>
       </c>
       <c r="L54" s="39" t="n">
         <f aca="false">IF($I$5=1,L67,L80)</f>
-        <v>-0.122539558482664</v>
+        <v>0</v>
       </c>
       <c r="M54" s="39" t="n">
         <f aca="false">IF($I$5=1,M67,M80)</f>
-        <v>0.10674816544916</v>
+        <v>0.163374</v>
       </c>
       <c r="N54" s="39" t="n">
         <f aca="false">IF($I$5=1,N67,N80)</f>
-        <v>0.229497603197751</v>
+        <v>0.830109</v>
       </c>
       <c r="O54" s="39" t="n">
         <f aca="false">IF($I$5=1,O67,O80)</f>
-        <v>0.055925553662358</v>
+        <v>0</v>
       </c>
       <c r="P54" s="39" t="n">
         <f aca="false">IF($I$5=1,P67,P80)</f>
-        <v>-0.0245559368280542</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="40" t="n">
         <f aca="false">SUM(I54:P54)</f>
@@ -22683,35 +22683,35 @@
       </c>
       <c r="I55" s="39" t="n">
         <f aca="false">IF($I$5=1,I68,I81)</f>
-        <v>0.524368932869297</v>
+        <v>0</v>
       </c>
       <c r="J55" s="39" t="n">
         <f aca="false">IF($I$5=1,J68,J81)</f>
-        <v>-0.0608329039123656</v>
+        <v>0</v>
       </c>
       <c r="K55" s="39" t="n">
         <f aca="false">IF($I$5=1,K68,K81)</f>
-        <v>0.293914481945607</v>
+        <v>0</v>
       </c>
       <c r="L55" s="39" t="n">
         <f aca="false">IF($I$5=1,L68,L81)</f>
-        <v>-0.124690543549074</v>
+        <v>0</v>
       </c>
       <c r="M55" s="39" t="n">
         <f aca="false">IF($I$5=1,M68,M81)</f>
-        <v>0.10772485967818</v>
+        <v>0.087903</v>
       </c>
       <c r="N55" s="39" t="n">
         <f aca="false">IF($I$5=1,N68,N81)</f>
-        <v>0.231758768794809</v>
+        <v>0.912097</v>
       </c>
       <c r="O55" s="39" t="n">
         <f aca="false">IF($I$5=1,O68,O81)</f>
-        <v>0.0555356698871915</v>
+        <v>0</v>
       </c>
       <c r="P55" s="39" t="n">
         <f aca="false">IF($I$5=1,P68,P81)</f>
-        <v>-0.0277792657136448</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="40" t="n">
         <f aca="false">SUM(I55:P55)</f>
@@ -22728,35 +22728,35 @@
       </c>
       <c r="I56" s="39" t="n">
         <f aca="false">IF($I$5=1,I69,I82)</f>
-        <v>0.528379419679543</v>
+        <v>0</v>
       </c>
       <c r="J56" s="39" t="n">
         <f aca="false">IF($I$5=1,J69,J82)</f>
-        <v>-0.0639388785210929</v>
+        <v>0</v>
       </c>
       <c r="K56" s="39" t="n">
         <f aca="false">IF($I$5=1,K69,K82)</f>
-        <v>0.295536307645177</v>
+        <v>0</v>
       </c>
       <c r="L56" s="39" t="n">
         <f aca="false">IF($I$5=1,L69,L82)</f>
-        <v>-0.126841528615483</v>
+        <v>0</v>
       </c>
       <c r="M56" s="39" t="n">
         <f aca="false">IF($I$5=1,M69,M82)</f>
-        <v>0.108701553907201</v>
+        <v>0</v>
       </c>
       <c r="N56" s="39" t="n">
         <f aca="false">IF($I$5=1,N69,N82)</f>
-        <v>0.234019934391866</v>
+        <v>1</v>
       </c>
       <c r="O56" s="39" t="n">
         <f aca="false">IF($I$5=1,O69,O82)</f>
-        <v>0.055145786112025</v>
+        <v>0</v>
       </c>
       <c r="P56" s="39" t="n">
         <f aca="false">IF($I$5=1,P69,P82)</f>
-        <v>-0.0310025945992354</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="40" t="n">
         <f aca="false">SUM(I56:P56)</f>
@@ -23648,7 +23648,7 @@
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H91" s="8" t="n">
         <f aca="false">$I$12</f>
-        <v>0.0122217948332109</v>
+        <v>0.0172079118776168</v>
       </c>
       <c r="I91" s="23" t="n">
         <f aca="false">$I$7</f>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="N91" s="8" t="n">
         <f aca="false">MAX($I$19:$I$27)</f>
-        <v>0.0122217948332109</v>
+        <v>0.0172079118776168</v>
       </c>
       <c r="O91" s="23" t="n">
         <f aca="false">MAX($J$19:$J$27)</f>
@@ -23677,11 +23677,11 @@
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H92" s="8" t="n">
         <f aca="false">1.5*$I$12</f>
-        <v>0.0183326922498164</v>
+        <v>0.0258118678164251</v>
       </c>
       <c r="I92" s="23" t="n">
         <f aca="false">$I$14+1.5*($I$7-$I$14)</f>
-        <v>0.0901813732038144</v>
+        <v>0.0901813732038145</v>
       </c>
       <c r="K92" s="43" t="n">
         <v>1.5</v>
@@ -23696,7 +23696,7 @@
       </c>
       <c r="N92" s="8" t="n">
         <f aca="false">MAX($I$19:$I$27)</f>
-        <v>0.0122217948332109</v>
+        <v>0.0172079118776168</v>
       </c>
       <c r="O92" s="23" t="n">
         <f aca="false">$I$14</f>
